--- a/data/CM-AM AVENIR ACTIONS FRANCE.xlsx
+++ b/data/CM-AM AVENIR ACTIONS FRANCE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t>Historique Cours</t>
   </si>
@@ -20,37 +20,55 @@
     <t>Date d'export</t>
   </si>
   <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>Valeur :</t>
+  </si>
+  <si>
+    <t>Libellé valeur :</t>
+  </si>
+  <si>
+    <t>Code Isin :</t>
+  </si>
+  <si>
+    <t>AVENIR ACT. FRANCE</t>
+  </si>
+  <si>
+    <t>000010001411</t>
+  </si>
+  <si>
+    <t>Se rendre en bas du document</t>
+  </si>
+  <si>
+    <t>Date de cotation</t>
+  </si>
+  <si>
+    <t>Dernier cours en EUR</t>
+  </si>
+  <si>
+    <t>Evolution en %</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
     <t>31/10/2025</t>
-  </si>
-  <si>
-    <t>Valeur :</t>
-  </si>
-  <si>
-    <t>Libellé valeur :</t>
-  </si>
-  <si>
-    <t>Code Isin :</t>
-  </si>
-  <si>
-    <t>AVENIR ACT. FRANCE</t>
-  </si>
-  <si>
-    <t>000010001411</t>
-  </si>
-  <si>
-    <t>Se rendre en bas du document</t>
-  </si>
-  <si>
-    <t>Date de cotation</t>
-  </si>
-  <si>
-    <t>Dernier cours en EUR</t>
-  </si>
-  <si>
-    <t>Evolution en %</t>
-  </si>
-  <si>
-    <t>Volume</t>
   </si>
   <si>
     <t>30/09/2025</t>
@@ -907,8 +925,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D205" headerRowCount="1">
-  <autoFilter ref="A7:D205"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D211" headerRowCount="1">
+  <autoFilter ref="A7:D211"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Date de cotation"/>
     <tableColumn id="2" name="Dernier cours en EUR"/>
@@ -921,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1" style="1"/>
@@ -1035,13 +1053,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="14">
-        <v>31.822</v>
+        <v>30.5481</v>
       </c>
       <c r="C8" s="15">
-        <v>2.08</v>
+        <v>-9.29</v>
       </c>
       <c r="D8" s="16">
-        <v>1880093</v>
+        <v>1845420</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1051,13 +1069,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="14">
-        <v>31.1747</v>
+        <v>33.6778</v>
       </c>
       <c r="C9" s="15">
-        <v>-1.94</v>
+        <v>4.78</v>
       </c>
       <c r="D9" s="16">
-        <v>1899842</v>
+        <v>1841711</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1067,13 +1085,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="14">
-        <v>31.7929</v>
+        <v>32.1402</v>
       </c>
       <c r="C10" s="15">
-        <v>0.74</v>
+        <v>-0.65</v>
       </c>
       <c r="D10" s="16">
-        <v>1895409</v>
+        <v>1853038</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1083,13 +1101,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="14">
-        <v>31.5594</v>
+        <v>32.3488</v>
       </c>
       <c r="C11" s="15">
-        <v>-1.11</v>
+        <v>0.41</v>
       </c>
       <c r="D11" s="16">
-        <v>1887049</v>
+        <v>1856067</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1099,13 +1117,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="14">
-        <v>31.9149</v>
+        <v>32.2171</v>
       </c>
       <c r="C12" s="15">
-        <v>3.82</v>
+        <v>-0.16</v>
       </c>
       <c r="D12" s="16">
-        <v>1868057</v>
+        <v>1851156</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1115,13 +1133,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="14">
-        <v>30.7409</v>
+        <v>32.269</v>
       </c>
       <c r="C13" s="15">
-        <v>-1.28</v>
+        <v>1.41</v>
       </c>
       <c r="D13" s="16">
-        <v>1811378</v>
+        <v>1858235</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1131,13 +1149,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="14">
-        <v>31.1391</v>
+        <v>31.822</v>
       </c>
       <c r="C14" s="15">
-        <v>-2.83</v>
+        <v>2.08</v>
       </c>
       <c r="D14" s="16">
-        <v>1787831</v>
+        <v>1880093</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1147,13 +1165,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="14">
-        <v>32.0467</v>
+        <v>31.1747</v>
       </c>
       <c r="C15" s="15">
-        <v>1.45</v>
+        <v>-1.94</v>
       </c>
       <c r="D15" s="16">
-        <v>1781034</v>
+        <v>1899842</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1163,13 +1181,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="14">
-        <v>31.589</v>
+        <v>31.7929</v>
       </c>
       <c r="C16" s="15">
-        <v>7.74</v>
+        <v>0.74</v>
       </c>
       <c r="D16" s="16">
-        <v>1795264</v>
+        <v>1895409</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1179,13 +1197,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="14">
-        <v>29.3208</v>
+        <v>31.5594</v>
       </c>
       <c r="C17" s="15">
-        <v>1.95</v>
+        <v>-1.11</v>
       </c>
       <c r="D17" s="16">
-        <v>1812931</v>
+        <v>1887049</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1195,13 +1213,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="14">
-        <v>28.7613</v>
+        <v>31.9149</v>
       </c>
       <c r="C18" s="15">
-        <v>-1.53</v>
+        <v>3.82</v>
       </c>
       <c r="D18" s="16">
-        <v>1837168</v>
+        <v>1868057</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1211,13 +1229,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="14">
-        <v>29.2094</v>
+        <v>30.7409</v>
       </c>
       <c r="C19" s="15">
-        <v>-3.79</v>
+        <v>-1.28</v>
       </c>
       <c r="D19" s="16">
-        <v>1854897</v>
+        <v>1811378</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1227,13 +1245,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="14">
-        <v>30.3597</v>
+        <v>31.1391</v>
       </c>
       <c r="C20" s="15">
-        <v>-0.46</v>
+        <v>-2.83</v>
       </c>
       <c r="D20" s="16">
-        <v>1866664</v>
+        <v>1787831</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1243,13 +1261,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="14">
-        <v>30.4995</v>
+        <v>32.0467</v>
       </c>
       <c r="C21" s="15">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="D21" s="16">
-        <v>1849732</v>
+        <v>1781034</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1259,13 +1277,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="14">
-        <v>30.177</v>
+        <v>31.589</v>
       </c>
       <c r="C22" s="15">
-        <v>1.19</v>
+        <v>7.74</v>
       </c>
       <c r="D22" s="16">
-        <v>1812757</v>
+        <v>1795264</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1275,13 +1293,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="14">
-        <v>29.8232</v>
+        <v>29.3208</v>
       </c>
       <c r="C23" s="15">
-        <v>-6.56</v>
+        <v>1.95</v>
       </c>
       <c r="D23" s="16">
-        <v>1823657</v>
+        <v>1812931</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1291,13 +1309,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="14">
-        <v>31.9162</v>
+        <v>28.7613</v>
       </c>
       <c r="C24" s="15">
-        <v>2.25</v>
+        <v>-1.53</v>
       </c>
       <c r="D24" s="16">
-        <v>1804431</v>
+        <v>1837168</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1307,13 +1325,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="14">
-        <v>31.2153</v>
+        <v>29.2094</v>
       </c>
       <c r="C25" s="15">
-        <v>-2.57</v>
+        <v>-3.79</v>
       </c>
       <c r="D25" s="16">
-        <v>1718427</v>
+        <v>1854897</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1323,13 +1341,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="14">
-        <v>32.0383</v>
+        <v>30.3597</v>
       </c>
       <c r="C26" s="15">
-        <v>3.72</v>
+        <v>-0.46</v>
       </c>
       <c r="D26" s="16">
-        <v>1715025</v>
+        <v>1866664</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -1339,13 +1357,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="14">
-        <v>30.8889</v>
+        <v>30.4995</v>
       </c>
       <c r="C27" s="15">
-        <v>2.71</v>
+        <v>1.07</v>
       </c>
       <c r="D27" s="16">
-        <v>1694204</v>
+        <v>1849732</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -1355,13 +1373,13 @@
         <v>33</v>
       </c>
       <c r="B28" s="14">
-        <v>30.0734</v>
+        <v>30.177</v>
       </c>
       <c r="C28" s="15">
-        <v>2.44</v>
+        <v>1.19</v>
       </c>
       <c r="D28" s="16">
-        <v>1695516</v>
+        <v>1812757</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -1371,13 +1389,13 @@
         <v>34</v>
       </c>
       <c r="B29" s="14">
-        <v>29.3584</v>
+        <v>29.8232</v>
       </c>
       <c r="C29" s="15">
-        <v>3.18</v>
+        <v>-6.56</v>
       </c>
       <c r="D29" s="16">
-        <v>1677345</v>
+        <v>1823657</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1387,13 +1405,13 @@
         <v>35</v>
       </c>
       <c r="B30" s="14">
-        <v>28.4531</v>
+        <v>31.9162</v>
       </c>
       <c r="C30" s="15">
-        <v>6.56</v>
+        <v>2.25</v>
       </c>
       <c r="D30" s="16">
-        <v>1676134</v>
+        <v>1804431</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1403,13 +1421,13 @@
         <v>36</v>
       </c>
       <c r="B31" s="14">
-        <v>26.7023</v>
+        <v>31.2153</v>
       </c>
       <c r="C31" s="15">
-        <v>-5.03</v>
+        <v>-2.57</v>
       </c>
       <c r="D31" s="16">
-        <v>1681792</v>
+        <v>1718427</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -1419,13 +1437,13 @@
         <v>37</v>
       </c>
       <c r="B32" s="14">
-        <v>28.1177</v>
+        <v>32.0383</v>
       </c>
       <c r="C32" s="15">
-        <v>-2.77</v>
+        <v>3.72</v>
       </c>
       <c r="D32" s="16">
-        <v>1680995</v>
+        <v>1715025</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
@@ -1435,13 +1453,13 @@
         <v>38</v>
       </c>
       <c r="B33" s="14">
-        <v>28.9179</v>
+        <v>30.8889</v>
       </c>
       <c r="C33" s="15">
-        <v>-2.63</v>
+        <v>2.71</v>
       </c>
       <c r="D33" s="16">
-        <v>1651309</v>
+        <v>1694204</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1451,13 +1469,13 @@
         <v>39</v>
       </c>
       <c r="B34" s="14">
-        <v>29.6987</v>
+        <v>30.0734</v>
       </c>
       <c r="C34" s="15">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="D34" s="16">
-        <v>1732322</v>
+        <v>1695516</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1467,13 +1485,13 @@
         <v>40</v>
       </c>
       <c r="B35" s="14">
-        <v>29.2216</v>
+        <v>29.3584</v>
       </c>
       <c r="C35" s="15">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="D35" s="16">
-        <v>1722587</v>
+        <v>1677345</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -1483,13 +1501,13 @@
         <v>41</v>
       </c>
       <c r="B36" s="14">
-        <v>28.1138</v>
+        <v>28.4531</v>
       </c>
       <c r="C36" s="15">
-        <v>-3.78</v>
+        <v>6.56</v>
       </c>
       <c r="D36" s="16">
-        <v>1598562</v>
+        <v>1676134</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1499,13 +1517,13 @@
         <v>42</v>
       </c>
       <c r="B37" s="14">
-        <v>29.217</v>
+        <v>26.7023</v>
       </c>
       <c r="C37" s="15">
-        <v>2.41</v>
+        <v>-5.03</v>
       </c>
       <c r="D37" s="16">
-        <v>1454774</v>
+        <v>1681792</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -1515,13 +1533,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="14">
-        <v>28.5297</v>
+        <v>28.1177</v>
       </c>
       <c r="C38" s="15">
-        <v>-0.92</v>
+        <v>-2.77</v>
       </c>
       <c r="D38" s="16">
-        <v>1416314</v>
+        <v>1680995</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -1531,13 +1549,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="14">
-        <v>28.7945</v>
+        <v>28.9179</v>
       </c>
       <c r="C39" s="15">
-        <v>2.3</v>
+        <v>-2.63</v>
       </c>
       <c r="D39" s="16">
-        <v>1410593</v>
+        <v>1651309</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -1547,13 +1565,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="14">
-        <v>28.1481</v>
+        <v>29.6987</v>
       </c>
       <c r="C40" s="15">
-        <v>9.55</v>
+        <v>1.63</v>
       </c>
       <c r="D40" s="16">
-        <v>1387780</v>
+        <v>1732322</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -1563,13 +1581,13 @@
         <v>46</v>
       </c>
       <c r="B41" s="14">
-        <v>25.6943</v>
+        <v>29.2216</v>
       </c>
       <c r="C41" s="15">
-        <v>-3.92</v>
+        <v>3.94</v>
       </c>
       <c r="D41" s="16">
-        <v>1375352</v>
+        <v>1722587</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -1579,13 +1597,13 @@
         <v>47</v>
       </c>
       <c r="B42" s="14">
-        <v>26.7429</v>
+        <v>28.1138</v>
       </c>
       <c r="C42" s="15">
-        <v>7.21</v>
+        <v>-3.78</v>
       </c>
       <c r="D42" s="16">
-        <v>1366161</v>
+        <v>1598562</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1595,13 +1613,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="14">
-        <v>24.9445</v>
+        <v>29.217</v>
       </c>
       <c r="C43" s="15">
-        <v>7.66</v>
+        <v>2.41</v>
       </c>
       <c r="D43" s="16">
-        <v>1351135</v>
+        <v>1454774</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -1611,13 +1629,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="14">
-        <v>23.1704</v>
+        <v>28.5297</v>
       </c>
       <c r="C44" s="15">
-        <v>-6.41</v>
+        <v>-0.92</v>
       </c>
       <c r="D44" s="16">
-        <v>1375553</v>
+        <v>1416314</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -1627,13 +1645,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="14">
-        <v>24.7583</v>
+        <v>28.7945</v>
       </c>
       <c r="C45" s="15">
-        <v>-4.99</v>
+        <v>2.3</v>
       </c>
       <c r="D45" s="16">
-        <v>1384429</v>
+        <v>1410593</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -1643,13 +1661,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="14">
-        <v>26.0581</v>
+        <v>28.1481</v>
       </c>
       <c r="C46" s="15">
-        <v>8.95</v>
+        <v>9.55</v>
       </c>
       <c r="D46" s="16">
-        <v>1381585</v>
+        <v>1387780</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -1659,13 +1677,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="14">
-        <v>23.9169</v>
+        <v>25.6943</v>
       </c>
       <c r="C47" s="15">
-        <v>-8.57</v>
+        <v>-3.92</v>
       </c>
       <c r="D47" s="16">
-        <v>1371863</v>
+        <v>1375352</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -1675,13 +1693,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="14">
-        <v>26.1594</v>
+        <v>26.7429</v>
       </c>
       <c r="C48" s="15">
-        <v>-0.12</v>
+        <v>7.21</v>
       </c>
       <c r="D48" s="16">
-        <v>1287343</v>
+        <v>1366161</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -1691,13 +1709,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="14">
-        <v>26.1909</v>
+        <v>24.9445</v>
       </c>
       <c r="C49" s="15">
-        <v>-1.72</v>
+        <v>7.66</v>
       </c>
       <c r="D49" s="16">
-        <v>1170403</v>
+        <v>1351135</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -1707,13 +1725,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="14">
-        <v>26.6484</v>
+        <v>23.1704</v>
       </c>
       <c r="C50" s="15">
-        <v>0.76</v>
+        <v>-6.41</v>
       </c>
       <c r="D50" s="16">
-        <v>1143247</v>
+        <v>1375553</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -1723,13 +1741,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="14">
-        <v>26.4469</v>
+        <v>24.7583</v>
       </c>
       <c r="C51" s="15">
-        <v>-5.76</v>
+        <v>-4.99</v>
       </c>
       <c r="D51" s="16">
-        <v>1137079</v>
+        <v>1384429</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -1739,13 +1757,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="14">
-        <v>28.0635</v>
+        <v>26.0581</v>
       </c>
       <c r="C52" s="15">
-        <v>-3.24</v>
+        <v>8.95</v>
       </c>
       <c r="D52" s="16">
-        <v>1141735</v>
+        <v>1381585</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -1755,13 +1773,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="14">
-        <v>29.0019</v>
+        <v>23.9169</v>
       </c>
       <c r="C53" s="15">
-        <v>5.74</v>
+        <v>-8.57</v>
       </c>
       <c r="D53" s="16">
-        <v>1140149</v>
+        <v>1371863</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1771,13 +1789,13 @@
         <v>59</v>
       </c>
       <c r="B54" s="14">
-        <v>27.4275</v>
+        <v>26.1594</v>
       </c>
       <c r="C54" s="15">
-        <v>-2.25</v>
+        <v>-0.12</v>
       </c>
       <c r="D54" s="16">
-        <v>1132208</v>
+        <v>1287343</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -1787,13 +1805,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="14">
-        <v>28.0597</v>
+        <v>26.1909</v>
       </c>
       <c r="C55" s="15">
-        <v>3.46</v>
+        <v>-1.72</v>
       </c>
       <c r="D55" s="16">
-        <v>1147749</v>
+        <v>1170403</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -1803,13 +1821,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="14">
-        <v>27.1204</v>
+        <v>26.6484</v>
       </c>
       <c r="C56" s="15">
-        <v>-2.46</v>
+        <v>0.76</v>
       </c>
       <c r="D56" s="16">
-        <v>1152596</v>
+        <v>1143247</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -1819,13 +1837,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="14">
-        <v>27.803</v>
+        <v>26.4469</v>
       </c>
       <c r="C57" s="15">
-        <v>1.38</v>
+        <v>-5.76</v>
       </c>
       <c r="D57" s="16">
-        <v>1154198</v>
+        <v>1137079</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -1835,13 +1853,13 @@
         <v>63</v>
       </c>
       <c r="B58" s="14">
-        <v>27.4252</v>
+        <v>28.0635</v>
       </c>
       <c r="C58" s="15">
-        <v>2.14</v>
+        <v>-3.24</v>
       </c>
       <c r="D58" s="16">
-        <v>1150734</v>
+        <v>1141735</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -1851,13 +1869,13 @@
         <v>64</v>
       </c>
       <c r="B59" s="14">
-        <v>26.8514</v>
+        <v>29.0019</v>
       </c>
       <c r="C59" s="15">
-        <v>0.99</v>
+        <v>5.74</v>
       </c>
       <c r="D59" s="16">
-        <v>1153800</v>
+        <v>1140149</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -1867,13 +1885,13 @@
         <v>65</v>
       </c>
       <c r="B60" s="14">
-        <v>26.5879</v>
+        <v>27.4275</v>
       </c>
       <c r="C60" s="15">
-        <v>3.19</v>
+        <v>-2.25</v>
       </c>
       <c r="D60" s="16">
-        <v>1101557</v>
+        <v>1132208</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -1883,13 +1901,13 @@
         <v>66</v>
       </c>
       <c r="B61" s="14">
-        <v>25.7667</v>
+        <v>28.0597</v>
       </c>
       <c r="C61" s="15">
-        <v>3.09</v>
+        <v>3.46</v>
       </c>
       <c r="D61" s="16">
-        <v>1014341</v>
+        <v>1147749</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -1899,13 +1917,13 @@
         <v>67</v>
       </c>
       <c r="B62" s="14">
-        <v>24.9942</v>
+        <v>27.1204</v>
       </c>
       <c r="C62" s="15">
-        <v>6.62</v>
+        <v>-2.46</v>
       </c>
       <c r="D62" s="16">
-        <v>1008521</v>
+        <v>1152596</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -1915,13 +1933,13 @@
         <v>68</v>
       </c>
       <c r="B63" s="14">
-        <v>23.4425</v>
+        <v>27.803</v>
       </c>
       <c r="C63" s="15">
-        <v>4.78</v>
+        <v>1.38</v>
       </c>
       <c r="D63" s="16">
-        <v>996086</v>
+        <v>1154198</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -1931,13 +1949,13 @@
         <v>69</v>
       </c>
       <c r="B64" s="14">
-        <v>22.3735</v>
+        <v>27.4252</v>
       </c>
       <c r="C64" s="15">
-        <v>-2.49</v>
+        <v>2.14</v>
       </c>
       <c r="D64" s="16">
-        <v>936620</v>
+        <v>1150734</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -1947,13 +1965,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="14">
-        <v>22.9443</v>
+        <v>26.8514</v>
       </c>
       <c r="C65" s="15">
-        <v>0.46</v>
+        <v>0.99</v>
       </c>
       <c r="D65" s="16">
-        <v>943879</v>
+        <v>1153800</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -1963,13 +1981,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="14">
-        <v>22.8391</v>
+        <v>26.5879</v>
       </c>
       <c r="C66" s="15">
-        <v>19.72</v>
+        <v>3.19</v>
       </c>
       <c r="D66" s="16">
-        <v>941803</v>
+        <v>1101557</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -1979,13 +1997,13 @@
         <v>72</v>
       </c>
       <c r="B67" s="14">
-        <v>19.0775</v>
+        <v>25.7667</v>
       </c>
       <c r="C67" s="15">
-        <v>-5.12</v>
+        <v>3.09</v>
       </c>
       <c r="D67" s="16">
-        <v>955223</v>
+        <v>1014341</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -1995,13 +2013,13 @@
         <v>73</v>
       </c>
       <c r="B68" s="14">
-        <v>20.1067</v>
+        <v>24.9942</v>
       </c>
       <c r="C68" s="15">
-        <v>-2.83</v>
+        <v>6.62</v>
       </c>
       <c r="D68" s="16">
-        <v>964204</v>
+        <v>1008521</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -2011,13 +2029,13 @@
         <v>74</v>
       </c>
       <c r="B69" s="14">
-        <v>20.6927</v>
+        <v>23.4425</v>
       </c>
       <c r="C69" s="15">
-        <v>3.04</v>
+        <v>4.78</v>
       </c>
       <c r="D69" s="16">
-        <v>966711</v>
+        <v>996086</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -2027,13 +2045,13 @@
         <v>75</v>
       </c>
       <c r="B70" s="14">
-        <v>20.0818</v>
+        <v>22.3735</v>
       </c>
       <c r="C70" s="15">
-        <v>-2.08</v>
+        <v>-2.49</v>
       </c>
       <c r="D70" s="16">
-        <v>972275</v>
+        <v>936620</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -2043,13 +2061,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="14">
-        <v>20.5081</v>
+        <v>22.9443</v>
       </c>
       <c r="C71" s="15">
-        <v>5.22</v>
+        <v>0.46</v>
       </c>
       <c r="D71" s="16">
-        <v>969359</v>
+        <v>943879</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -2059,13 +2077,13 @@
         <v>77</v>
       </c>
       <c r="B72" s="14">
-        <v>19.4916</v>
+        <v>22.8391</v>
       </c>
       <c r="C72" s="15">
-        <v>3.37</v>
+        <v>19.72</v>
       </c>
       <c r="D72" s="16">
-        <v>931780</v>
+        <v>941803</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -2075,13 +2093,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="14">
-        <v>18.8562</v>
+        <v>19.0775</v>
       </c>
       <c r="C73" s="15">
-        <v>4.26</v>
+        <v>-5.12</v>
       </c>
       <c r="D73" s="16">
-        <v>867387</v>
+        <v>955223</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
@@ -2091,13 +2109,13 @@
         <v>79</v>
       </c>
       <c r="B74" s="14">
-        <v>18.0866</v>
+        <v>20.1067</v>
       </c>
       <c r="C74" s="15">
-        <v>-17.9</v>
+        <v>-2.83</v>
       </c>
       <c r="D74" s="16">
-        <v>841914</v>
+        <v>964204</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
@@ -2107,13 +2125,13 @@
         <v>80</v>
       </c>
       <c r="B75" s="14">
-        <v>22.0299</v>
+        <v>20.6927</v>
       </c>
       <c r="C75" s="15">
-        <v>-8.09</v>
+        <v>3.04</v>
       </c>
       <c r="D75" s="16">
-        <v>857939</v>
+        <v>966711</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
@@ -2123,13 +2141,13 @@
         <v>81</v>
       </c>
       <c r="B76" s="14">
-        <v>23.9688</v>
+        <v>20.0818</v>
       </c>
       <c r="C76" s="15">
-        <v>-3.01</v>
+        <v>-2.08</v>
       </c>
       <c r="D76" s="16">
-        <v>858061</v>
+        <v>972275</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
@@ -2139,13 +2157,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="14">
-        <v>24.7119</v>
+        <v>20.5081</v>
       </c>
       <c r="C77" s="15">
-        <v>1.35</v>
+        <v>5.22</v>
       </c>
       <c r="D77" s="16">
-        <v>855605</v>
+        <v>969359</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
@@ -2155,13 +2173,13 @@
         <v>83</v>
       </c>
       <c r="B78" s="14">
-        <v>24.3826</v>
+        <v>19.4916</v>
       </c>
       <c r="C78" s="15">
-        <v>2.71</v>
+        <v>3.37</v>
       </c>
       <c r="D78" s="16">
-        <v>846151</v>
+        <v>931780</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -2171,13 +2189,13 @@
         <v>84</v>
       </c>
       <c r="B79" s="14">
-        <v>23.7392</v>
+        <v>18.8562</v>
       </c>
       <c r="C79" s="15">
-        <v>0.72</v>
+        <v>4.26</v>
       </c>
       <c r="D79" s="16">
-        <v>841907</v>
+        <v>867387</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
@@ -2187,13 +2205,13 @@
         <v>85</v>
       </c>
       <c r="B80" s="14">
-        <v>23.5698</v>
+        <v>18.0866</v>
       </c>
       <c r="C80" s="15">
-        <v>3.73</v>
+        <v>-17.9</v>
       </c>
       <c r="D80" s="16">
-        <v>845465</v>
+        <v>841914</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
@@ -2203,13 +2221,13 @@
         <v>86</v>
       </c>
       <c r="B81" s="14">
-        <v>22.7222</v>
+        <v>22.0299</v>
       </c>
       <c r="C81" s="15">
-        <v>-1.07</v>
+        <v>-8.09</v>
       </c>
       <c r="D81" s="16">
-        <v>851371</v>
+        <v>857939</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2219,13 +2237,13 @@
         <v>87</v>
       </c>
       <c r="B82" s="14">
-        <v>22.9686</v>
+        <v>23.9688</v>
       </c>
       <c r="C82" s="15">
-        <v>-0.43</v>
+        <v>-3.01</v>
       </c>
       <c r="D82" s="16">
-        <v>854459</v>
+        <v>858061</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
@@ -2235,13 +2253,13 @@
         <v>88</v>
       </c>
       <c r="B83" s="14">
-        <v>23.0684</v>
+        <v>24.7119</v>
       </c>
       <c r="C83" s="15">
-        <v>6.75</v>
+        <v>1.35</v>
       </c>
       <c r="D83" s="16">
-        <v>847628</v>
+        <v>855605</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
@@ -2251,13 +2269,13 @@
         <v>89</v>
       </c>
       <c r="B84" s="14">
-        <v>21.6108</v>
+        <v>24.3826</v>
       </c>
       <c r="C84" s="15">
-        <v>-5.23</v>
+        <v>2.71</v>
       </c>
       <c r="D84" s="16">
-        <v>803441</v>
+        <v>846151</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
@@ -2267,13 +2285,13 @@
         <v>90</v>
       </c>
       <c r="B85" s="14">
-        <v>22.8026</v>
+        <v>23.7392</v>
       </c>
       <c r="C85" s="15">
-        <v>4.74</v>
+        <v>0.72</v>
       </c>
       <c r="D85" s="16">
-        <v>718935</v>
+        <v>841907</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
@@ -2283,13 +2301,13 @@
         <v>91</v>
       </c>
       <c r="B86" s="14">
-        <v>21.7712</v>
+        <v>23.5698</v>
       </c>
       <c r="C86" s="15">
-        <v>2.2</v>
+        <v>3.73</v>
       </c>
       <c r="D86" s="16">
-        <v>688109</v>
+        <v>845465</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
@@ -2299,13 +2317,13 @@
         <v>92</v>
       </c>
       <c r="B87" s="14">
-        <v>21.303</v>
+        <v>22.7222</v>
       </c>
       <c r="C87" s="15">
-        <v>5.38</v>
+        <v>-1.07</v>
       </c>
       <c r="D87" s="16">
-        <v>681469</v>
+        <v>851371</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2315,13 +2333,13 @@
         <v>93</v>
       </c>
       <c r="B88" s="14">
-        <v>20.215</v>
+        <v>22.9686</v>
       </c>
       <c r="C88" s="15">
-        <v>5.2</v>
+        <v>-0.43</v>
       </c>
       <c r="D88" s="16">
-        <v>667101</v>
+        <v>854459</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
@@ -2331,13 +2349,13 @@
         <v>94</v>
       </c>
       <c r="B89" s="14">
-        <v>19.2165</v>
+        <v>23.0684</v>
       </c>
       <c r="C89" s="15">
-        <v>-5.94</v>
+        <v>6.75</v>
       </c>
       <c r="D89" s="16">
-        <v>667383</v>
+        <v>847628</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -2347,13 +2365,13 @@
         <v>95</v>
       </c>
       <c r="B90" s="14">
-        <v>20.4298</v>
+        <v>21.6108</v>
       </c>
       <c r="C90" s="15">
-        <v>-1.76</v>
+        <v>-5.23</v>
       </c>
       <c r="D90" s="16">
-        <v>669111</v>
+        <v>803441</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -2363,13 +2381,13 @@
         <v>96</v>
       </c>
       <c r="B91" s="14">
-        <v>20.7954</v>
+        <v>22.8026</v>
       </c>
       <c r="C91" s="15">
-        <v>-6.97</v>
+        <v>4.74</v>
       </c>
       <c r="D91" s="16">
-        <v>665867</v>
+        <v>718935</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -2379,13 +2397,13 @@
         <v>97</v>
       </c>
       <c r="B92" s="14">
-        <v>22.3534</v>
+        <v>21.7712</v>
       </c>
       <c r="C92" s="15">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="D92" s="16">
-        <v>665362</v>
+        <v>688109</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -2395,13 +2413,13 @@
         <v>98</v>
       </c>
       <c r="B93" s="14">
-        <v>22.006</v>
+        <v>21.303</v>
       </c>
       <c r="C93" s="15">
-        <v>-2.1</v>
+        <v>5.38</v>
       </c>
       <c r="D93" s="16">
-        <v>664905</v>
+        <v>681469</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -2411,13 +2429,13 @@
         <v>99</v>
       </c>
       <c r="B94" s="14">
-        <v>22.4772</v>
+        <v>20.215</v>
       </c>
       <c r="C94" s="15">
-        <v>3.04</v>
+        <v>5.2</v>
       </c>
       <c r="D94" s="16">
-        <v>666304</v>
+        <v>667101</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
@@ -2427,13 +2445,13 @@
         <v>100</v>
       </c>
       <c r="B95" s="14">
-        <v>21.8133</v>
+        <v>19.2165</v>
       </c>
       <c r="C95" s="15">
-        <v>-0.8</v>
+        <v>-5.94</v>
       </c>
       <c r="D95" s="16">
-        <v>649857</v>
+        <v>667383</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
@@ -2443,13 +2461,13 @@
         <v>101</v>
       </c>
       <c r="B96" s="14">
-        <v>21.9894</v>
+        <v>20.4298</v>
       </c>
       <c r="C96" s="15">
-        <v>-0.4</v>
+        <v>-1.76</v>
       </c>
       <c r="D96" s="16">
-        <v>644418</v>
+        <v>669111</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
@@ -2459,13 +2477,13 @@
         <v>102</v>
       </c>
       <c r="B97" s="14">
-        <v>22.0767</v>
+        <v>20.7954</v>
       </c>
       <c r="C97" s="15">
-        <v>6.38</v>
+        <v>-6.97</v>
       </c>
       <c r="D97" s="16">
-        <v>604788</v>
+        <v>665867</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -2475,13 +2493,13 @@
         <v>103</v>
       </c>
       <c r="B98" s="14">
-        <v>20.752</v>
+        <v>22.3534</v>
       </c>
       <c r="C98" s="15">
-        <v>-2.44</v>
+        <v>1.58</v>
       </c>
       <c r="D98" s="16">
-        <v>593084</v>
+        <v>665362</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -2491,13 +2509,13 @@
         <v>104</v>
       </c>
       <c r="B99" s="14">
-        <v>21.2709</v>
+        <v>22.006</v>
       </c>
       <c r="C99" s="15">
-        <v>-2.82</v>
+        <v>-2.1</v>
       </c>
       <c r="D99" s="16">
-        <v>583239</v>
+        <v>664905</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -2507,13 +2525,13 @@
         <v>105</v>
       </c>
       <c r="B100" s="14">
-        <v>21.889</v>
+        <v>22.4772</v>
       </c>
       <c r="C100" s="15">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="D100" s="16">
-        <v>575763</v>
+        <v>666304</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -2523,13 +2541,13 @@
         <v>106</v>
       </c>
       <c r="B101" s="14">
-        <v>21.2419</v>
+        <v>21.8133</v>
       </c>
       <c r="C101" s="15">
-        <v>-1.14</v>
+        <v>-0.8</v>
       </c>
       <c r="D101" s="16">
-        <v>556044</v>
+        <v>649857</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
@@ -2539,13 +2557,13 @@
         <v>107</v>
       </c>
       <c r="B102" s="14">
-        <v>21.4864</v>
+        <v>21.9894</v>
       </c>
       <c r="C102" s="15">
-        <v>-2.49</v>
+        <v>-0.4</v>
       </c>
       <c r="D102" s="16">
-        <v>543886</v>
+        <v>644418</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
@@ -2555,13 +2573,13 @@
         <v>108</v>
       </c>
       <c r="B103" s="14">
-        <v>22.0356</v>
+        <v>22.0767</v>
       </c>
       <c r="C103" s="15">
-        <v>2.6</v>
+        <v>6.38</v>
       </c>
       <c r="D103" s="16">
-        <v>536700</v>
+        <v>604788</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -2571,13 +2589,13 @@
         <v>109</v>
       </c>
       <c r="B104" s="14">
-        <v>21.478</v>
+        <v>20.752</v>
       </c>
       <c r="C104" s="15">
-        <v>4.69</v>
+        <v>-2.44</v>
       </c>
       <c r="D104" s="16">
-        <v>525076</v>
+        <v>593084</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
@@ -2587,13 +2605,13 @@
         <v>110</v>
       </c>
       <c r="B105" s="14">
-        <v>20.5167</v>
+        <v>21.2709</v>
       </c>
       <c r="C105" s="15">
-        <v>-0.41</v>
+        <v>-2.82</v>
       </c>
       <c r="D105" s="16">
-        <v>517170</v>
+        <v>583239</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -2603,13 +2621,13 @@
         <v>111</v>
       </c>
       <c r="B106" s="14">
-        <v>20.6018</v>
+        <v>21.889</v>
       </c>
       <c r="C106" s="15">
-        <v>-0.41</v>
+        <v>3.05</v>
       </c>
       <c r="D106" s="16">
-        <v>516385</v>
+        <v>575763</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
@@ -2619,13 +2637,13 @@
         <v>112</v>
       </c>
       <c r="B107" s="14">
-        <v>20.6865</v>
+        <v>21.2419</v>
       </c>
       <c r="C107" s="15">
-        <v>-2.72</v>
+        <v>-1.14</v>
       </c>
       <c r="D107" s="16">
-        <v>515324</v>
+        <v>556044</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
@@ -2635,13 +2653,13 @@
         <v>113</v>
       </c>
       <c r="B108" s="14">
-        <v>21.2641</v>
+        <v>21.4864</v>
       </c>
       <c r="C108" s="15">
-        <v>1.87</v>
+        <v>-2.49</v>
       </c>
       <c r="D108" s="16">
-        <v>494739</v>
+        <v>543886</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
@@ -2651,13 +2669,13 @@
         <v>114</v>
       </c>
       <c r="B109" s="14">
-        <v>20.8729</v>
+        <v>22.0356</v>
       </c>
       <c r="C109" s="15">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="D109" s="16">
-        <v>449488</v>
+        <v>536700</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
@@ -2667,13 +2685,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="14">
-        <v>20.2105</v>
+        <v>21.478</v>
       </c>
       <c r="C110" s="15">
-        <v>5.39</v>
+        <v>4.69</v>
       </c>
       <c r="D110" s="16">
-        <v>439668</v>
+        <v>525076</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
@@ -2683,13 +2701,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="14">
-        <v>19.1772</v>
+        <v>20.5167</v>
       </c>
       <c r="C111" s="15">
-        <v>2.19</v>
+        <v>-0.41</v>
       </c>
       <c r="D111" s="16">
-        <v>431165</v>
+        <v>517170</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
@@ -2699,13 +2717,13 @@
         <v>117</v>
       </c>
       <c r="B112" s="14">
-        <v>18.7654</v>
+        <v>20.6018</v>
       </c>
       <c r="C112" s="15">
-        <v>-2.24</v>
+        <v>-0.41</v>
       </c>
       <c r="D112" s="16">
-        <v>422201</v>
+        <v>516385</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
@@ -2715,13 +2733,13 @@
         <v>118</v>
       </c>
       <c r="B113" s="14">
-        <v>19.1954</v>
+        <v>20.6865</v>
       </c>
       <c r="C113" s="15">
-        <v>6.55</v>
+        <v>-2.72</v>
       </c>
       <c r="D113" s="16">
-        <v>425382</v>
+        <v>515324</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
@@ -2731,13 +2749,13 @@
         <v>119</v>
       </c>
       <c r="B114" s="14">
-        <v>18.0154</v>
+        <v>21.2641</v>
       </c>
       <c r="C114" s="15">
-        <v>0.93</v>
+        <v>1.87</v>
       </c>
       <c r="D114" s="16">
-        <v>421039</v>
+        <v>494739</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
@@ -2747,13 +2765,13 @@
         <v>120</v>
       </c>
       <c r="B115" s="14">
-        <v>17.849</v>
+        <v>20.8729</v>
       </c>
       <c r="C115" s="15">
-        <v>1.31</v>
+        <v>3.28</v>
       </c>
       <c r="D115" s="16">
-        <v>425552</v>
+        <v>449488</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -2763,13 +2781,13 @@
         <v>121</v>
       </c>
       <c r="B116" s="14">
-        <v>17.6184</v>
+        <v>20.2105</v>
       </c>
       <c r="C116" s="15">
-        <v>-0.34</v>
+        <v>5.39</v>
       </c>
       <c r="D116" s="16">
-        <v>429235</v>
+        <v>439668</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
@@ -2779,13 +2797,13 @@
         <v>122</v>
       </c>
       <c r="B117" s="14">
-        <v>17.6784</v>
+        <v>19.1772</v>
       </c>
       <c r="C117" s="15">
-        <v>-0.02</v>
+        <v>2.19</v>
       </c>
       <c r="D117" s="16">
-        <v>431025</v>
+        <v>431165</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
@@ -2795,13 +2813,13 @@
         <v>123</v>
       </c>
       <c r="B118" s="14">
-        <v>17.6823</v>
+        <v>18.7654</v>
       </c>
       <c r="C118" s="15">
-        <v>4.21</v>
+        <v>-2.24</v>
       </c>
       <c r="D118" s="16">
-        <v>427073</v>
+        <v>422201</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
@@ -2811,13 +2829,13 @@
         <v>124</v>
       </c>
       <c r="B119" s="14">
-        <v>16.9676</v>
+        <v>19.1954</v>
       </c>
       <c r="C119" s="15">
-        <v>-5.59</v>
+        <v>6.55</v>
       </c>
       <c r="D119" s="16">
-        <v>423611</v>
+        <v>425382</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
@@ -2827,13 +2845,13 @@
         <v>125</v>
       </c>
       <c r="B120" s="14">
-        <v>17.9726</v>
+        <v>18.0154</v>
       </c>
       <c r="C120" s="15">
-        <v>3.29</v>
+        <v>0.93</v>
       </c>
       <c r="D120" s="16">
-        <v>406589</v>
+        <v>421039</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
@@ -2843,13 +2861,13 @@
         <v>126</v>
       </c>
       <c r="B121" s="14">
-        <v>17.401</v>
+        <v>17.849</v>
       </c>
       <c r="C121" s="15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="D121" s="16">
-        <v>383668</v>
+        <v>425552</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
@@ -2859,13 +2877,13 @@
         <v>127</v>
       </c>
       <c r="B122" s="14">
-        <v>17.1786</v>
+        <v>17.6184</v>
       </c>
       <c r="C122" s="15">
-        <v>0.93</v>
+        <v>-0.34</v>
       </c>
       <c r="D122" s="16">
-        <v>383404</v>
+        <v>429235</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
@@ -2875,13 +2893,13 @@
         <v>128</v>
       </c>
       <c r="B123" s="14">
-        <v>17.0211</v>
+        <v>17.6784</v>
       </c>
       <c r="C123" s="15">
-        <v>-1.23</v>
+        <v>-0.02</v>
       </c>
       <c r="D123" s="16">
-        <v>369347</v>
+        <v>431025</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -2891,13 +2909,13 @@
         <v>129</v>
       </c>
       <c r="B124" s="14">
-        <v>17.2327</v>
+        <v>17.6823</v>
       </c>
       <c r="C124" s="15">
-        <v>-4.57</v>
+        <v>4.21</v>
       </c>
       <c r="D124" s="16">
-        <v>365521</v>
+        <v>427073</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
@@ -2907,13 +2925,13 @@
         <v>130</v>
       </c>
       <c r="B125" s="14">
-        <v>18.0587</v>
+        <v>16.9676</v>
       </c>
       <c r="C125" s="15">
-        <v>-5.97</v>
+        <v>-5.59</v>
       </c>
       <c r="D125" s="16">
-        <v>351951</v>
+        <v>423611</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -2923,13 +2941,13 @@
         <v>131</v>
       </c>
       <c r="B126" s="14">
-        <v>19.2059</v>
+        <v>17.9726</v>
       </c>
       <c r="C126" s="15">
-        <v>1.7</v>
+        <v>3.29</v>
       </c>
       <c r="D126" s="16">
-        <v>329812</v>
+        <v>406589</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
@@ -2939,13 +2957,13 @@
         <v>132</v>
       </c>
       <c r="B127" s="14">
-        <v>18.8858</v>
+        <v>17.401</v>
       </c>
       <c r="C127" s="15">
-        <v>9.54</v>
+        <v>1.3</v>
       </c>
       <c r="D127" s="16">
-        <v>332262</v>
+        <v>383668</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
@@ -2955,13 +2973,13 @@
         <v>133</v>
       </c>
       <c r="B128" s="14">
-        <v>17.2404</v>
+        <v>17.1786</v>
       </c>
       <c r="C128" s="15">
-        <v>-4.1</v>
+        <v>0.93</v>
       </c>
       <c r="D128" s="16">
-        <v>334394</v>
+        <v>383404</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
@@ -2971,13 +2989,13 @@
         <v>134</v>
       </c>
       <c r="B129" s="14">
-        <v>17.9771</v>
+        <v>17.0211</v>
       </c>
       <c r="C129" s="15">
-        <v>-7.71</v>
+        <v>-1.23</v>
       </c>
       <c r="D129" s="16">
-        <v>334775</v>
+        <v>369347</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
@@ -2987,13 +3005,13 @@
         <v>135</v>
       </c>
       <c r="B130" s="14">
-        <v>19.4794</v>
+        <v>17.2327</v>
       </c>
       <c r="C130" s="15">
-        <v>5.85</v>
+        <v>-4.57</v>
       </c>
       <c r="D130" s="16">
-        <v>331859</v>
+        <v>365521</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
@@ -3003,13 +3021,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="14">
-        <v>18.4037</v>
+        <v>18.0587</v>
       </c>
       <c r="C131" s="15">
-        <v>-3.92</v>
+        <v>-5.97</v>
       </c>
       <c r="D131" s="16">
-        <v>331398</v>
+        <v>351951</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
@@ -3019,13 +3037,13 @@
         <v>137</v>
       </c>
       <c r="B132" s="14">
-        <v>19.1537</v>
+        <v>19.2059</v>
       </c>
       <c r="C132" s="15">
-        <v>0.67</v>
+        <v>1.7</v>
       </c>
       <c r="D132" s="16">
-        <v>324977</v>
+        <v>329812</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
@@ -3035,13 +3053,13 @@
         <v>138</v>
       </c>
       <c r="B133" s="14">
-        <v>19.0263</v>
+        <v>18.8858</v>
       </c>
       <c r="C133" s="15">
-        <v>0.89</v>
+        <v>9.54</v>
       </c>
       <c r="D133" s="16">
-        <v>317273</v>
+        <v>332262</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
@@ -3051,13 +3069,13 @@
         <v>139</v>
       </c>
       <c r="B134" s="14">
-        <v>18.8585</v>
+        <v>17.2404</v>
       </c>
       <c r="C134" s="15">
-        <v>1.95</v>
+        <v>-4.1</v>
       </c>
       <c r="D134" s="16">
-        <v>315938</v>
+        <v>334394</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
@@ -3067,13 +3085,13 @@
         <v>140</v>
       </c>
       <c r="B135" s="14">
-        <v>18.4986</v>
+        <v>17.9771</v>
       </c>
       <c r="C135" s="15">
-        <v>7.39</v>
+        <v>-7.71</v>
       </c>
       <c r="D135" s="16">
-        <v>321090</v>
+        <v>334775</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
@@ -3083,13 +3101,13 @@
         <v>141</v>
       </c>
       <c r="B136" s="14">
-        <v>17.2265</v>
+        <v>19.4794</v>
       </c>
       <c r="C136" s="15">
-        <v>7.47</v>
+        <v>5.85</v>
       </c>
       <c r="D136" s="16">
-        <v>313313</v>
+        <v>331859</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
@@ -3099,13 +3117,13 @@
         <v>142</v>
       </c>
       <c r="B137" s="14">
-        <v>16.0299</v>
+        <v>18.4037</v>
       </c>
       <c r="C137" s="15">
-        <v>-2.26</v>
+        <v>-3.92</v>
       </c>
       <c r="D137" s="16">
-        <v>307702</v>
+        <v>331398</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
@@ -3115,13 +3133,13 @@
         <v>143</v>
       </c>
       <c r="B138" s="14">
-        <v>16.4006</v>
+        <v>19.1537</v>
       </c>
       <c r="C138" s="15">
-        <v>4.09</v>
+        <v>0.67</v>
       </c>
       <c r="D138" s="16">
-        <v>314807</v>
+        <v>324977</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
@@ -3131,13 +3149,13 @@
         <v>144</v>
       </c>
       <c r="B139" s="14">
-        <v>15.7564</v>
+        <v>19.0263</v>
       </c>
       <c r="C139" s="15">
-        <v>-3.91</v>
+        <v>0.89</v>
       </c>
       <c r="D139" s="16">
-        <v>313983</v>
+        <v>317273</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
@@ -3147,13 +3165,13 @@
         <v>145</v>
       </c>
       <c r="B140" s="14">
-        <v>16.3969</v>
+        <v>18.8585</v>
       </c>
       <c r="C140" s="15">
-        <v>0.58</v>
+        <v>1.95</v>
       </c>
       <c r="D140" s="16">
-        <v>317840</v>
+        <v>315938</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
@@ -3163,13 +3181,13 @@
         <v>146</v>
       </c>
       <c r="B141" s="14">
-        <v>16.3023</v>
+        <v>18.4986</v>
       </c>
       <c r="C141" s="15">
-        <v>1.99</v>
+        <v>7.39</v>
       </c>
       <c r="D141" s="16">
-        <v>319776</v>
+        <v>321090</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
@@ -3179,13 +3197,13 @@
         <v>147</v>
       </c>
       <c r="B142" s="14">
-        <v>15.9839</v>
+        <v>17.2265</v>
       </c>
       <c r="C142" s="15">
-        <v>-3.62</v>
+        <v>7.47</v>
       </c>
       <c r="D142" s="16">
-        <v>326712</v>
+        <v>313313</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
@@ -3195,13 +3213,13 @@
         <v>148</v>
       </c>
       <c r="B143" s="14">
-        <v>16.585</v>
+        <v>16.0299</v>
       </c>
       <c r="C143" s="15">
-        <v>-1.81</v>
+        <v>-2.26</v>
       </c>
       <c r="D143" s="16">
-        <v>326835</v>
+        <v>307702</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
@@ -3211,13 +3229,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="14">
-        <v>16.89</v>
+        <v>16.4006</v>
       </c>
       <c r="C144" s="15">
-        <v>2.12</v>
+        <v>4.09</v>
       </c>
       <c r="D144" s="16">
-        <v>316759</v>
+        <v>314807</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
@@ -3227,13 +3245,13 @@
         <v>150</v>
       </c>
       <c r="B145" s="14">
-        <v>16.5388</v>
+        <v>15.7564</v>
       </c>
       <c r="C145" s="15">
-        <v>2</v>
+        <v>-3.91</v>
       </c>
       <c r="D145" s="16">
-        <v>311960</v>
+        <v>313983</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
@@ -3243,13 +3261,13 @@
         <v>151</v>
       </c>
       <c r="B146" s="14">
-        <v>16.2147</v>
+        <v>16.3969</v>
       </c>
       <c r="C146" s="15">
-        <v>0.02</v>
+        <v>0.58</v>
       </c>
       <c r="D146" s="16">
-        <v>299481</v>
+        <v>317840</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
@@ -3259,13 +3277,13 @@
         <v>152</v>
       </c>
       <c r="B147" s="14">
-        <v>16.212</v>
+        <v>16.3023</v>
       </c>
       <c r="C147" s="15">
-        <v>5.71</v>
+        <v>1.99</v>
       </c>
       <c r="D147" s="16">
-        <v>299583</v>
+        <v>319776</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
@@ -3275,13 +3293,13 @@
         <v>153</v>
       </c>
       <c r="B148" s="14">
-        <v>15.336</v>
+        <v>15.9839</v>
       </c>
       <c r="C148" s="15">
-        <v>-2.61</v>
+        <v>-3.62</v>
       </c>
       <c r="D148" s="16">
-        <v>295466</v>
+        <v>326712</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
@@ -3291,13 +3309,13 @@
         <v>154</v>
       </c>
       <c r="B149" s="14">
-        <v>15.7463</v>
+        <v>16.585</v>
       </c>
       <c r="C149" s="15">
-        <v>0.38</v>
+        <v>-1.81</v>
       </c>
       <c r="D149" s="16">
-        <v>296547</v>
+        <v>326835</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
@@ -3307,13 +3325,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="14">
-        <v>15.6861</v>
+        <v>16.89</v>
       </c>
       <c r="C150" s="15">
-        <v>0.54</v>
+        <v>2.12</v>
       </c>
       <c r="D150" s="16">
-        <v>292185</v>
+        <v>316759</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
@@ -3323,13 +3341,13 @@
         <v>156</v>
       </c>
       <c r="B151" s="14">
-        <v>15.6022</v>
+        <v>16.5388</v>
       </c>
       <c r="C151" s="15">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="D151" s="16">
-        <v>291815</v>
+        <v>311960</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
@@ -3339,13 +3357,13 @@
         <v>157</v>
       </c>
       <c r="B152" s="14">
-        <v>15.0304</v>
+        <v>16.2147</v>
       </c>
       <c r="C152" s="15">
-        <v>5.47</v>
+        <v>0.02</v>
       </c>
       <c r="D152" s="16">
-        <v>287293</v>
+        <v>299481</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
@@ -3355,13 +3373,13 @@
         <v>158</v>
       </c>
       <c r="B153" s="14">
-        <v>14.2508</v>
+        <v>16.212</v>
       </c>
       <c r="C153" s="15">
-        <v>-1.6</v>
+        <v>5.71</v>
       </c>
       <c r="D153" s="16">
-        <v>285409</v>
+        <v>299583</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
@@ -3371,13 +3389,13 @@
         <v>159</v>
       </c>
       <c r="B154" s="14">
-        <v>14.4826</v>
+        <v>15.336</v>
       </c>
       <c r="C154" s="15">
-        <v>6.81</v>
+        <v>-2.61</v>
       </c>
       <c r="D154" s="16">
-        <v>288332</v>
+        <v>295466</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
@@ -3387,13 +3405,13 @@
         <v>160</v>
       </c>
       <c r="B155" s="14">
-        <v>13.5591</v>
+        <v>15.7463</v>
       </c>
       <c r="C155" s="15">
-        <v>-4.69</v>
+        <v>0.38</v>
       </c>
       <c r="D155" s="16">
-        <v>294120</v>
+        <v>296547</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
@@ -3403,13 +3421,13 @@
         <v>161</v>
       </c>
       <c r="B156" s="14">
-        <v>14.2262</v>
+        <v>15.6861</v>
       </c>
       <c r="C156" s="15">
-        <v>4.31</v>
+        <v>0.54</v>
       </c>
       <c r="D156" s="16">
-        <v>277446</v>
+        <v>292185</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
@@ -3419,13 +3437,13 @@
         <v>162</v>
       </c>
       <c r="B157" s="14">
-        <v>13.6383</v>
+        <v>15.6022</v>
       </c>
       <c r="C157" s="15">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="D157" s="16">
-        <v>273642</v>
+        <v>291815</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
@@ -3435,13 +3453,13 @@
         <v>163</v>
       </c>
       <c r="B158" s="14">
-        <v>13.2675</v>
+        <v>15.0304</v>
       </c>
       <c r="C158" s="15">
-        <v>-0.49</v>
+        <v>5.47</v>
       </c>
       <c r="D158" s="16">
-        <v>273311</v>
+        <v>287293</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
@@ -3451,13 +3469,13 @@
         <v>164</v>
       </c>
       <c r="B159" s="14">
-        <v>13.3332</v>
+        <v>14.2508</v>
       </c>
       <c r="C159" s="15">
-        <v>0.41</v>
+        <v>-1.6</v>
       </c>
       <c r="D159" s="16">
-        <v>269139</v>
+        <v>285409</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
@@ -3467,13 +3485,13 @@
         <v>165</v>
       </c>
       <c r="B160" s="14">
-        <v>13.2786</v>
+        <v>14.4826</v>
       </c>
       <c r="C160" s="15">
-        <v>2.66</v>
+        <v>6.81</v>
       </c>
       <c r="D160" s="16">
-        <v>263037</v>
+        <v>288332</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
@@ -3483,13 +3501,13 @@
         <v>166</v>
       </c>
       <c r="B161" s="14">
-        <v>12.9342</v>
+        <v>13.5591</v>
       </c>
       <c r="C161" s="15">
-        <v>2.04</v>
+        <v>-4.69</v>
       </c>
       <c r="D161" s="16">
-        <v>198754</v>
+        <v>294120</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
@@ -3499,13 +3517,13 @@
         <v>167</v>
       </c>
       <c r="B162" s="14">
-        <v>12.6757</v>
+        <v>14.2262</v>
       </c>
       <c r="C162" s="15">
-        <v>3.87</v>
+        <v>4.31</v>
       </c>
       <c r="D162" s="16">
-        <v>199980</v>
+        <v>277446</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
@@ -3515,13 +3533,13 @@
         <v>168</v>
       </c>
       <c r="B163" s="14">
-        <v>12.204</v>
+        <v>13.6383</v>
       </c>
       <c r="C163" s="15">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="D163" s="16">
-        <v>200970</v>
+        <v>273642</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
@@ -3531,13 +3549,13 @@
         <v>169</v>
       </c>
       <c r="B164" s="14">
-        <v>12.0241</v>
+        <v>13.2675</v>
       </c>
       <c r="C164" s="15">
-        <v>-1.24</v>
+        <v>-0.49</v>
       </c>
       <c r="D164" s="16">
-        <v>202101</v>
+        <v>273311</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
@@ -3547,13 +3565,13 @@
         <v>170</v>
       </c>
       <c r="B165" s="14">
-        <v>12.1748</v>
+        <v>13.3332</v>
       </c>
       <c r="C165" s="15">
-        <v>3.88</v>
+        <v>0.41</v>
       </c>
       <c r="D165" s="16">
-        <v>198314</v>
+        <v>269139</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
@@ -3563,13 +3581,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="14">
-        <v>11.7197</v>
+        <v>13.2786</v>
       </c>
       <c r="C166" s="15">
         <v>2.66</v>
       </c>
       <c r="D166" s="16">
-        <v>200713</v>
+        <v>263037</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
@@ -3579,13 +3597,13 @@
         <v>172</v>
       </c>
       <c r="B167" s="14">
-        <v>11.416</v>
+        <v>12.9342</v>
       </c>
       <c r="C167" s="15">
-        <v>5.97</v>
+        <v>2.04</v>
       </c>
       <c r="D167" s="16">
-        <v>213425</v>
+        <v>198754</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
@@ -3595,13 +3613,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="14">
-        <v>10.7726</v>
+        <v>12.6757</v>
       </c>
       <c r="C168" s="15">
-        <v>-4.57</v>
+        <v>3.87</v>
       </c>
       <c r="D168" s="16">
-        <v>210390</v>
+        <v>199980</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
@@ -3611,13 +3629,13 @@
         <v>174</v>
       </c>
       <c r="B169" s="14">
-        <v>11.2888</v>
+        <v>12.204</v>
       </c>
       <c r="C169" s="15">
-        <v>-4.75</v>
+        <v>1.5</v>
       </c>
       <c r="D169" s="16">
-        <v>206365</v>
+        <v>200970</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
@@ -3627,13 +3645,13 @@
         <v>175</v>
       </c>
       <c r="B170" s="14">
-        <v>11.852</v>
+        <v>12.0241</v>
       </c>
       <c r="C170" s="15">
-        <v>-0.58</v>
+        <v>-1.24</v>
       </c>
       <c r="D170" s="16">
-        <v>157507</v>
+        <v>202101</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
@@ -3643,13 +3661,13 @@
         <v>176</v>
       </c>
       <c r="B171" s="14">
-        <v>11.9208</v>
+        <v>12.1748</v>
       </c>
       <c r="C171" s="15">
-        <v>4.82</v>
+        <v>3.88</v>
       </c>
       <c r="D171" s="16">
-        <v>160205</v>
+        <v>198314</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
@@ -3659,13 +3677,13 @@
         <v>177</v>
       </c>
       <c r="B172" s="14">
-        <v>11.3722</v>
+        <v>11.7197</v>
       </c>
       <c r="C172" s="15">
-        <v>3.79</v>
+        <v>2.66</v>
       </c>
       <c r="D172" s="16">
-        <v>150268</v>
+        <v>200713</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
@@ -3675,13 +3693,13 @@
         <v>178</v>
       </c>
       <c r="B173" s="14">
-        <v>10.9572</v>
+        <v>11.416</v>
       </c>
       <c r="C173" s="15">
-        <v>0.42</v>
+        <v>5.97</v>
       </c>
       <c r="D173" s="16">
-        <v>153441</v>
+        <v>213425</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
@@ -3691,13 +3709,13 @@
         <v>179</v>
       </c>
       <c r="B174" s="14">
-        <v>10.9114</v>
+        <v>10.7726</v>
       </c>
       <c r="C174" s="15">
-        <v>-2.66</v>
+        <v>-4.57</v>
       </c>
       <c r="D174" s="16">
-        <v>151631</v>
+        <v>210390</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
@@ -3707,13 +3725,13 @@
         <v>180</v>
       </c>
       <c r="B175" s="14">
-        <v>11.2095</v>
+        <v>11.2888</v>
       </c>
       <c r="C175" s="15">
-        <v>8.56</v>
+        <v>-4.75</v>
       </c>
       <c r="D175" s="16">
-        <v>142871</v>
+        <v>206365</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="12"/>
@@ -3723,13 +3741,13 @@
         <v>181</v>
       </c>
       <c r="B176" s="14">
-        <v>10.3257</v>
+        <v>11.852</v>
       </c>
       <c r="C176" s="15">
-        <v>-8.54</v>
+        <v>-0.58</v>
       </c>
       <c r="D176" s="16">
-        <v>141565</v>
+        <v>157507</v>
       </c>
       <c r="E176" s="12"/>
       <c r="F176" s="12"/>
@@ -3739,13 +3757,13 @@
         <v>182</v>
       </c>
       <c r="B177" s="14">
-        <v>11.2894</v>
+        <v>11.9208</v>
       </c>
       <c r="C177" s="15">
-        <v>-10.9</v>
+        <v>4.82</v>
       </c>
       <c r="D177" s="16">
-        <v>141871</v>
+        <v>160205</v>
       </c>
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
@@ -3755,13 +3773,13 @@
         <v>183</v>
       </c>
       <c r="B178" s="14">
-        <v>12.6702</v>
+        <v>11.3722</v>
       </c>
       <c r="C178" s="15">
-        <v>-6.98</v>
+        <v>3.79</v>
       </c>
       <c r="D178" s="16">
-        <v>139960</v>
+        <v>150268</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
@@ -3771,13 +3789,13 @@
         <v>184</v>
       </c>
       <c r="B179" s="14">
-        <v>13.6202</v>
+        <v>10.9572</v>
       </c>
       <c r="C179" s="15">
-        <v>-0.31</v>
+        <v>0.42</v>
       </c>
       <c r="D179" s="16">
-        <v>139096</v>
+        <v>153441</v>
       </c>
       <c r="E179" s="12"/>
       <c r="F179" s="12"/>
@@ -3787,13 +3805,13 @@
         <v>185</v>
       </c>
       <c r="B180" s="14">
-        <v>13.662</v>
+        <v>10.9114</v>
       </c>
       <c r="C180" s="15">
-        <v>-0.77</v>
+        <v>-2.66</v>
       </c>
       <c r="D180" s="16">
-        <v>135452</v>
+        <v>151631</v>
       </c>
       <c r="E180" s="12"/>
       <c r="F180" s="12"/>
@@ -3803,13 +3821,13 @@
         <v>186</v>
       </c>
       <c r="B181" s="14">
-        <v>13.7682</v>
+        <v>11.2095</v>
       </c>
       <c r="C181" s="15">
-        <v>3.05</v>
+        <v>8.56</v>
       </c>
       <c r="D181" s="16">
-        <v>131534</v>
+        <v>142871</v>
       </c>
       <c r="E181" s="12"/>
       <c r="F181" s="12"/>
@@ -3819,13 +3837,13 @@
         <v>187</v>
       </c>
       <c r="B182" s="14">
-        <v>13.3604</v>
+        <v>10.3257</v>
       </c>
       <c r="C182" s="15">
-        <v>-3.01</v>
+        <v>-8.54</v>
       </c>
       <c r="D182" s="16">
-        <v>131823</v>
+        <v>141565</v>
       </c>
       <c r="E182" s="12"/>
       <c r="F182" s="12"/>
@@ -3835,13 +3853,13 @@
         <v>188</v>
       </c>
       <c r="B183" s="14">
-        <v>13.7753</v>
+        <v>11.2894</v>
       </c>
       <c r="C183" s="15">
-        <v>2.41</v>
+        <v>-10.9</v>
       </c>
       <c r="D183" s="16">
-        <v>120727</v>
+        <v>141871</v>
       </c>
       <c r="E183" s="12"/>
       <c r="F183" s="12"/>
@@ -3851,13 +3869,13 @@
         <v>189</v>
       </c>
       <c r="B184" s="14">
-        <v>13.4515</v>
+        <v>12.6702</v>
       </c>
       <c r="C184" s="15">
-        <v>4.46</v>
+        <v>-6.98</v>
       </c>
       <c r="D184" s="16">
-        <v>130415</v>
+        <v>139960</v>
       </c>
       <c r="E184" s="12"/>
       <c r="F184" s="12"/>
@@ -3867,13 +3885,13 @@
         <v>190</v>
       </c>
       <c r="B185" s="14">
-        <v>12.8772</v>
+        <v>13.6202</v>
       </c>
       <c r="C185" s="15">
-        <v>5.03</v>
+        <v>-0.31</v>
       </c>
       <c r="D185" s="16">
-        <v>126257</v>
+        <v>139096</v>
       </c>
       <c r="E185" s="12"/>
       <c r="F185" s="12"/>
@@ -3883,13 +3901,13 @@
         <v>191</v>
       </c>
       <c r="B186" s="14">
-        <v>12.2604</v>
+        <v>13.662</v>
       </c>
       <c r="C186" s="15">
-        <v>-4.65</v>
+        <v>-0.77</v>
       </c>
       <c r="D186" s="16">
-        <v>130402</v>
+        <v>135452</v>
       </c>
       <c r="E186" s="12"/>
       <c r="F186" s="12"/>
@@ -3899,13 +3917,13 @@
         <v>192</v>
       </c>
       <c r="B187" s="14">
-        <v>12.8587</v>
+        <v>13.7682</v>
       </c>
       <c r="C187" s="15">
-        <v>3.71</v>
+        <v>3.05</v>
       </c>
       <c r="D187" s="16">
-        <v>116472</v>
+        <v>131534</v>
       </c>
       <c r="E187" s="12"/>
       <c r="F187" s="12"/>
@@ -3915,13 +3933,13 @@
         <v>193</v>
       </c>
       <c r="B188" s="14">
-        <v>12.3992</v>
+        <v>13.3604</v>
       </c>
       <c r="C188" s="15">
-        <v>6.58</v>
+        <v>-3.01</v>
       </c>
       <c r="D188" s="16">
-        <v>83474</v>
+        <v>131823</v>
       </c>
       <c r="E188" s="12"/>
       <c r="F188" s="12"/>
@@ -3931,13 +3949,13 @@
         <v>194</v>
       </c>
       <c r="B189" s="14">
-        <v>11.6337</v>
+        <v>13.7753</v>
       </c>
       <c r="C189" s="15">
-        <v>-4.02</v>
+        <v>2.41</v>
       </c>
       <c r="D189" s="16">
-        <v>82889</v>
+        <v>120727</v>
       </c>
       <c r="E189" s="12"/>
       <c r="F189" s="12"/>
@@ -3947,13 +3965,13 @@
         <v>195</v>
       </c>
       <c r="B190" s="14">
-        <v>12.1203</v>
+        <v>13.4515</v>
       </c>
       <c r="C190" s="15">
-        <v>5.98</v>
+        <v>4.46</v>
       </c>
       <c r="D190" s="16">
-        <v>82053</v>
+        <v>130415</v>
       </c>
       <c r="E190" s="12"/>
       <c r="F190" s="12"/>
@@ -3963,13 +3981,13 @@
         <v>196</v>
       </c>
       <c r="B191" s="14">
-        <v>11.4361</v>
+        <v>12.8772</v>
       </c>
       <c r="C191" s="15">
-        <v>-1.45</v>
+        <v>5.03</v>
       </c>
       <c r="D191" s="16">
-        <v>81049</v>
+        <v>126257</v>
       </c>
       <c r="E191" s="12"/>
       <c r="F191" s="12"/>
@@ -3979,13 +3997,13 @@
         <v>197</v>
       </c>
       <c r="B192" s="14">
-        <v>11.6048</v>
+        <v>12.2604</v>
       </c>
       <c r="C192" s="15">
-        <v>-5.46</v>
+        <v>-4.65</v>
       </c>
       <c r="D192" s="16">
-        <v>80218</v>
+        <v>130402</v>
       </c>
       <c r="E192" s="12"/>
       <c r="F192" s="12"/>
@@ -3995,13 +4013,13 @@
         <v>198</v>
       </c>
       <c r="B193" s="14">
-        <v>12.2754</v>
+        <v>12.8587</v>
       </c>
       <c r="C193" s="15">
-        <v>-3.45</v>
+        <v>3.71</v>
       </c>
       <c r="D193" s="16">
-        <v>82348</v>
+        <v>116472</v>
       </c>
       <c r="E193" s="12"/>
       <c r="F193" s="12"/>
@@ -4011,13 +4029,13 @@
         <v>199</v>
       </c>
       <c r="B194" s="14">
-        <v>12.7141</v>
+        <v>12.3992</v>
       </c>
       <c r="C194" s="15">
-        <v>6.98</v>
+        <v>6.58</v>
       </c>
       <c r="D194" s="16">
-        <v>81655</v>
+        <v>83474</v>
       </c>
       <c r="E194" s="12"/>
       <c r="F194" s="12"/>
@@ -4027,13 +4045,13 @@
         <v>200</v>
       </c>
       <c r="B195" s="14">
-        <v>11.8845</v>
+        <v>11.6337</v>
       </c>
       <c r="C195" s="15">
-        <v>-0.46</v>
+        <v>-4.02</v>
       </c>
       <c r="D195" s="16">
-        <v>75890</v>
+        <v>82889</v>
       </c>
       <c r="E195" s="12"/>
       <c r="F195" s="12"/>
@@ -4043,13 +4061,13 @@
         <v>201</v>
       </c>
       <c r="B196" s="14">
-        <v>11.9391</v>
+        <v>12.1203</v>
       </c>
       <c r="C196" s="15">
-        <v>-4.96</v>
+        <v>5.98</v>
       </c>
       <c r="D196" s="16">
-        <v>76219</v>
+        <v>82053</v>
       </c>
       <c r="E196" s="12"/>
       <c r="F196" s="12"/>
@@ -4059,13 +4077,13 @@
         <v>202</v>
       </c>
       <c r="B197" s="14">
-        <v>12.5625</v>
+        <v>11.4361</v>
       </c>
       <c r="C197" s="15">
-        <v>7.3</v>
+        <v>-1.45</v>
       </c>
       <c r="D197" s="16">
-        <v>76139</v>
+        <v>81049</v>
       </c>
       <c r="E197" s="12"/>
       <c r="F197" s="12"/>
@@ -4075,13 +4093,13 @@
         <v>203</v>
       </c>
       <c r="B198" s="14">
-        <v>11.7076</v>
+        <v>11.6048</v>
       </c>
       <c r="C198" s="15">
-        <v>1.96</v>
+        <v>-5.46</v>
       </c>
       <c r="D198" s="16">
-        <v>61820</v>
+        <v>80218</v>
       </c>
       <c r="E198" s="12"/>
       <c r="F198" s="12"/>
@@ -4091,13 +4109,13 @@
         <v>204</v>
       </c>
       <c r="B199" s="14">
-        <v>11.483</v>
+        <v>12.2754</v>
       </c>
       <c r="C199" s="15">
-        <v>-4.73</v>
+        <v>-3.45</v>
       </c>
       <c r="D199" s="16">
-        <v>59970</v>
+        <v>82348</v>
       </c>
       <c r="E199" s="12"/>
       <c r="F199" s="12"/>
@@ -4107,13 +4125,13 @@
         <v>205</v>
       </c>
       <c r="B200" s="14">
-        <v>12.053</v>
+        <v>12.7141</v>
       </c>
       <c r="C200" s="15">
-        <v>3.59</v>
+        <v>6.98</v>
       </c>
       <c r="D200" s="16">
-        <v>2002</v>
+        <v>81655</v>
       </c>
       <c r="E200" s="12"/>
       <c r="F200" s="12"/>
@@ -4123,13 +4141,13 @@
         <v>206</v>
       </c>
       <c r="B201" s="14">
-        <v>11.635</v>
+        <v>11.8845</v>
       </c>
       <c r="C201" s="15">
-        <v>5.73</v>
+        <v>-0.46</v>
       </c>
       <c r="D201" s="16">
-        <v>1947</v>
+        <v>75890</v>
       </c>
       <c r="E201" s="12"/>
       <c r="F201" s="12"/>
@@ -4139,13 +4157,13 @@
         <v>207</v>
       </c>
       <c r="B202" s="14">
-        <v>11.004</v>
+        <v>11.9391</v>
       </c>
       <c r="C202" s="15">
-        <v>8.56</v>
+        <v>-4.96</v>
       </c>
       <c r="D202" s="16">
-        <v>1919</v>
+        <v>76219</v>
       </c>
       <c r="E202" s="12"/>
       <c r="F202" s="12"/>
@@ -4155,13 +4173,13 @@
         <v>208</v>
       </c>
       <c r="B203" s="14">
-        <v>10.136</v>
+        <v>12.5625</v>
       </c>
       <c r="C203" s="15">
-        <v>-2.95</v>
+        <v>7.3</v>
       </c>
       <c r="D203" s="16">
-        <v>1911</v>
+        <v>76139</v>
       </c>
       <c r="E203" s="12"/>
       <c r="F203" s="12"/>
@@ -4171,13 +4189,13 @@
         <v>209</v>
       </c>
       <c r="B204" s="14">
-        <v>10.444</v>
+        <v>11.7076</v>
       </c>
       <c r="C204" s="15">
-        <v>4.44</v>
+        <v>1.96</v>
       </c>
       <c r="D204" s="16">
-        <v>232</v>
+        <v>61820</v>
       </c>
       <c r="E204" s="12"/>
       <c r="F204" s="12"/>
@@ -4187,29 +4205,125 @@
         <v>210</v>
       </c>
       <c r="B205" s="14">
-        <v>10</v>
-      </c>
-      <c r="C205" s="17" t="s">
-        <v>211</v>
+        <v>11.483</v>
+      </c>
+      <c r="C205" s="15">
+        <v>-4.73</v>
       </c>
       <c r="D205" s="16">
-        <v>0</v>
+        <v>59970</v>
       </c>
       <c r="E205" s="12"/>
       <c r="F205" s="12"/>
     </row>
-    <row r="206" ht="35" customHeight="1">
-      <c r="A206" s="18" t="s">
+    <row r="206" s="12" customFormat="1">
+      <c r="A206" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B206" s="14">
+        <v>12.053</v>
+      </c>
+      <c r="C206" s="15">
+        <v>3.59</v>
+      </c>
+      <c r="D206" s="16">
+        <v>2002</v>
+      </c>
+      <c r="E206" s="12"/>
+      <c r="F206" s="12"/>
+    </row>
+    <row r="207" s="12" customFormat="1">
+      <c r="A207" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B206" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C206" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="D206" s="18" t="s">
-        <v>212</v>
+      <c r="B207" s="14">
+        <v>11.635</v>
+      </c>
+      <c r="C207" s="15">
+        <v>5.73</v>
+      </c>
+      <c r="D207" s="16">
+        <v>1947</v>
+      </c>
+      <c r="E207" s="12"/>
+      <c r="F207" s="12"/>
+    </row>
+    <row r="208" s="12" customFormat="1">
+      <c r="A208" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B208" s="14">
+        <v>11.004</v>
+      </c>
+      <c r="C208" s="15">
+        <v>8.56</v>
+      </c>
+      <c r="D208" s="16">
+        <v>1919</v>
+      </c>
+      <c r="E208" s="12"/>
+      <c r="F208" s="12"/>
+    </row>
+    <row r="209" s="12" customFormat="1">
+      <c r="A209" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B209" s="14">
+        <v>10.136</v>
+      </c>
+      <c r="C209" s="15">
+        <v>-2.95</v>
+      </c>
+      <c r="D209" s="16">
+        <v>1911</v>
+      </c>
+      <c r="E209" s="12"/>
+      <c r="F209" s="12"/>
+    </row>
+    <row r="210" s="12" customFormat="1">
+      <c r="A210" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B210" s="14">
+        <v>10.444</v>
+      </c>
+      <c r="C210" s="15">
+        <v>4.44</v>
+      </c>
+      <c r="D210" s="16">
+        <v>232</v>
+      </c>
+      <c r="E210" s="12"/>
+      <c r="F210" s="12"/>
+    </row>
+    <row r="211" s="12" customFormat="1">
+      <c r="A211" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B211" s="14">
+        <v>10</v>
+      </c>
+      <c r="C211" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D211" s="16">
+        <v>0</v>
+      </c>
+      <c r="E211" s="12"/>
+      <c r="F211" s="12"/>
+    </row>
+    <row r="212" ht="35" customHeight="1">
+      <c r="A212" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C212" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D212" s="18" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4225,18 +4339,18 @@
     <mergeCell ref="E4:E4"/>
     <mergeCell ref="E5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A206:D206"/>
+    <mergeCell ref="A212:D212"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Historique Cours'!A206" display="Se rendre en bas du document"/>
-    <hyperlink ref="B6" location="'Historique Cours'!A206" display="Se rendre en bas du document"/>
-    <hyperlink ref="C6" location="'Historique Cours'!A206" display="Se rendre en bas du document"/>
-    <hyperlink ref="D6" location="'Historique Cours'!A206" display="Se rendre en bas du document"/>
-    <hyperlink ref="E6" location="'Historique Cours'!A206" display="Se rendre en bas du document"/>
-    <hyperlink ref="A206" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="B206" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="C206" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="D206" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="A6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
+    <hyperlink ref="B6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
+    <hyperlink ref="C6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
+    <hyperlink ref="D6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
+    <hyperlink ref="E6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
+    <hyperlink ref="A212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="B212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="C212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="D212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
   </hyperlinks>
   <headerFooter/>
   <tableParts>

--- a/data/CM-AM AVENIR ACTIONS FRANCE.xlsx
+++ b/data/CM-AM AVENIR ACTIONS FRANCE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>Historique Cours</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Date d'export</t>
   </si>
   <si>
-    <t>21/04/2026</t>
+    <t>21/10/2026</t>
   </si>
   <si>
     <t>Valeur :</t>
@@ -51,6 +51,24 @@
   </si>
   <si>
     <t>Volume</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
   </si>
   <si>
     <t>31/03/2026</t>
@@ -925,8 +943,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D211" headerRowCount="1">
-  <autoFilter ref="A7:D211"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableData_0_0" displayName="TableData_0_0" ref="A7:D217" headerRowCount="1">
+  <autoFilter ref="A7:D217"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Date de cotation"/>
     <tableColumn id="2" name="Dernier cours en EUR"/>
@@ -939,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1" style="1"/>
@@ -1053,13 +1071,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="14">
-        <v>30.5481</v>
+        <v>31.692</v>
       </c>
       <c r="C8" s="15">
-        <v>-9.29</v>
+        <v>-4.02</v>
       </c>
       <c r="D8" s="16">
-        <v>1845420</v>
+        <v>1907889</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1069,13 +1087,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="14">
-        <v>33.6778</v>
+        <v>33.0203</v>
       </c>
       <c r="C9" s="15">
-        <v>4.78</v>
+        <v>-2.13</v>
       </c>
       <c r="D9" s="16">
-        <v>1841711</v>
+        <v>1899239</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1085,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="14">
-        <v>32.1402</v>
+        <v>33.7392</v>
       </c>
       <c r="C10" s="15">
-        <v>-0.65</v>
+        <v>0.39</v>
       </c>
       <c r="D10" s="16">
-        <v>1853038</v>
+        <v>1907377</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1101,13 +1119,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="14">
-        <v>32.3488</v>
+        <v>33.6068</v>
       </c>
       <c r="C11" s="15">
-        <v>0.41</v>
+        <v>2.69</v>
       </c>
       <c r="D11" s="16">
-        <v>1856067</v>
+        <v>1900601</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1117,13 +1135,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="14">
-        <v>32.2171</v>
+        <v>32.7263</v>
       </c>
       <c r="C12" s="15">
-        <v>-0.16</v>
+        <v>2.37</v>
       </c>
       <c r="D12" s="16">
-        <v>1851156</v>
+        <v>1894320</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1133,13 +1151,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="14">
-        <v>32.269</v>
+        <v>31.9701</v>
       </c>
       <c r="C13" s="15">
-        <v>1.41</v>
+        <v>4.66</v>
       </c>
       <c r="D13" s="16">
-        <v>1858235</v>
+        <v>1852549</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1149,13 +1167,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="14">
-        <v>31.822</v>
+        <v>30.5481</v>
       </c>
       <c r="C14" s="15">
-        <v>2.08</v>
+        <v>-9.29</v>
       </c>
       <c r="D14" s="16">
-        <v>1880093</v>
+        <v>1845420</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1165,13 +1183,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="14">
-        <v>31.1747</v>
+        <v>33.6778</v>
       </c>
       <c r="C15" s="15">
-        <v>-1.94</v>
+        <v>4.78</v>
       </c>
       <c r="D15" s="16">
-        <v>1899842</v>
+        <v>1841711</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1181,13 +1199,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="14">
-        <v>31.7929</v>
+        <v>32.1402</v>
       </c>
       <c r="C16" s="15">
-        <v>0.74</v>
+        <v>-0.65</v>
       </c>
       <c r="D16" s="16">
-        <v>1895409</v>
+        <v>1853038</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1197,13 +1215,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="14">
-        <v>31.5594</v>
+        <v>32.3488</v>
       </c>
       <c r="C17" s="15">
-        <v>-1.11</v>
+        <v>0.41</v>
       </c>
       <c r="D17" s="16">
-        <v>1887049</v>
+        <v>1856067</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1213,13 +1231,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="14">
-        <v>31.9149</v>
+        <v>32.2171</v>
       </c>
       <c r="C18" s="15">
-        <v>3.82</v>
+        <v>-0.16</v>
       </c>
       <c r="D18" s="16">
-        <v>1868057</v>
+        <v>1851156</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1229,13 +1247,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="14">
-        <v>30.7409</v>
+        <v>32.269</v>
       </c>
       <c r="C19" s="15">
-        <v>-1.28</v>
+        <v>1.41</v>
       </c>
       <c r="D19" s="16">
-        <v>1811378</v>
+        <v>1858235</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1245,13 +1263,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="14">
-        <v>31.1391</v>
+        <v>31.822</v>
       </c>
       <c r="C20" s="15">
-        <v>-2.83</v>
+        <v>2.08</v>
       </c>
       <c r="D20" s="16">
-        <v>1787831</v>
+        <v>1880093</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1261,13 +1279,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="14">
-        <v>32.0467</v>
+        <v>31.1747</v>
       </c>
       <c r="C21" s="15">
-        <v>1.45</v>
+        <v>-1.94</v>
       </c>
       <c r="D21" s="16">
-        <v>1781034</v>
+        <v>1899842</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1277,13 +1295,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="14">
-        <v>31.589</v>
+        <v>31.7929</v>
       </c>
       <c r="C22" s="15">
-        <v>7.74</v>
+        <v>0.74</v>
       </c>
       <c r="D22" s="16">
-        <v>1795264</v>
+        <v>1895409</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1293,13 +1311,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="14">
-        <v>29.3208</v>
+        <v>31.5594</v>
       </c>
       <c r="C23" s="15">
-        <v>1.95</v>
+        <v>-1.11</v>
       </c>
       <c r="D23" s="16">
-        <v>1812931</v>
+        <v>1887049</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1309,13 +1327,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="14">
-        <v>28.7613</v>
+        <v>31.9149</v>
       </c>
       <c r="C24" s="15">
-        <v>-1.53</v>
+        <v>3.82</v>
       </c>
       <c r="D24" s="16">
-        <v>1837168</v>
+        <v>1868057</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1325,13 +1343,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="14">
-        <v>29.2094</v>
+        <v>30.7409</v>
       </c>
       <c r="C25" s="15">
-        <v>-3.79</v>
+        <v>-1.28</v>
       </c>
       <c r="D25" s="16">
-        <v>1854897</v>
+        <v>1811378</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1341,13 +1359,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="14">
-        <v>30.3597</v>
+        <v>31.1391</v>
       </c>
       <c r="C26" s="15">
-        <v>-0.46</v>
+        <v>-2.83</v>
       </c>
       <c r="D26" s="16">
-        <v>1866664</v>
+        <v>1787831</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -1357,13 +1375,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="14">
-        <v>30.4995</v>
+        <v>32.0467</v>
       </c>
       <c r="C27" s="15">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="D27" s="16">
-        <v>1849732</v>
+        <v>1781034</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -1373,13 +1391,13 @@
         <v>33</v>
       </c>
       <c r="B28" s="14">
-        <v>30.177</v>
+        <v>31.589</v>
       </c>
       <c r="C28" s="15">
-        <v>1.19</v>
+        <v>7.74</v>
       </c>
       <c r="D28" s="16">
-        <v>1812757</v>
+        <v>1795264</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -1389,13 +1407,13 @@
         <v>34</v>
       </c>
       <c r="B29" s="14">
-        <v>29.8232</v>
+        <v>29.3208</v>
       </c>
       <c r="C29" s="15">
-        <v>-6.56</v>
+        <v>1.95</v>
       </c>
       <c r="D29" s="16">
-        <v>1823657</v>
+        <v>1812931</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1405,13 +1423,13 @@
         <v>35</v>
       </c>
       <c r="B30" s="14">
-        <v>31.9162</v>
+        <v>28.7613</v>
       </c>
       <c r="C30" s="15">
-        <v>2.25</v>
+        <v>-1.53</v>
       </c>
       <c r="D30" s="16">
-        <v>1804431</v>
+        <v>1837168</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -1421,13 +1439,13 @@
         <v>36</v>
       </c>
       <c r="B31" s="14">
-        <v>31.2153</v>
+        <v>29.2094</v>
       </c>
       <c r="C31" s="15">
-        <v>-2.57</v>
+        <v>-3.79</v>
       </c>
       <c r="D31" s="16">
-        <v>1718427</v>
+        <v>1854897</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -1437,13 +1455,13 @@
         <v>37</v>
       </c>
       <c r="B32" s="14">
-        <v>32.0383</v>
+        <v>30.3597</v>
       </c>
       <c r="C32" s="15">
-        <v>3.72</v>
+        <v>-0.46</v>
       </c>
       <c r="D32" s="16">
-        <v>1715025</v>
+        <v>1866664</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
@@ -1453,13 +1471,13 @@
         <v>38</v>
       </c>
       <c r="B33" s="14">
-        <v>30.8889</v>
+        <v>30.4995</v>
       </c>
       <c r="C33" s="15">
-        <v>2.71</v>
+        <v>1.07</v>
       </c>
       <c r="D33" s="16">
-        <v>1694204</v>
+        <v>1849732</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1469,13 +1487,13 @@
         <v>39</v>
       </c>
       <c r="B34" s="14">
-        <v>30.0734</v>
+        <v>30.177</v>
       </c>
       <c r="C34" s="15">
-        <v>2.44</v>
+        <v>1.19</v>
       </c>
       <c r="D34" s="16">
-        <v>1695516</v>
+        <v>1812757</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -1485,13 +1503,13 @@
         <v>40</v>
       </c>
       <c r="B35" s="14">
-        <v>29.3584</v>
+        <v>29.8232</v>
       </c>
       <c r="C35" s="15">
-        <v>3.18</v>
+        <v>-6.56</v>
       </c>
       <c r="D35" s="16">
-        <v>1677345</v>
+        <v>1823657</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -1501,13 +1519,13 @@
         <v>41</v>
       </c>
       <c r="B36" s="14">
-        <v>28.4531</v>
+        <v>31.9162</v>
       </c>
       <c r="C36" s="15">
-        <v>6.56</v>
+        <v>2.25</v>
       </c>
       <c r="D36" s="16">
-        <v>1676134</v>
+        <v>1804431</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1517,13 +1535,13 @@
         <v>42</v>
       </c>
       <c r="B37" s="14">
-        <v>26.7023</v>
+        <v>31.2153</v>
       </c>
       <c r="C37" s="15">
-        <v>-5.03</v>
+        <v>-2.57</v>
       </c>
       <c r="D37" s="16">
-        <v>1681792</v>
+        <v>1718427</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -1533,13 +1551,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="14">
-        <v>28.1177</v>
+        <v>32.0383</v>
       </c>
       <c r="C38" s="15">
-        <v>-2.77</v>
+        <v>3.72</v>
       </c>
       <c r="D38" s="16">
-        <v>1680995</v>
+        <v>1715025</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -1549,13 +1567,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="14">
-        <v>28.9179</v>
+        <v>30.8889</v>
       </c>
       <c r="C39" s="15">
-        <v>-2.63</v>
+        <v>2.71</v>
       </c>
       <c r="D39" s="16">
-        <v>1651309</v>
+        <v>1694204</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -1565,13 +1583,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="14">
-        <v>29.6987</v>
+        <v>30.0734</v>
       </c>
       <c r="C40" s="15">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="D40" s="16">
-        <v>1732322</v>
+        <v>1695516</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -1581,13 +1599,13 @@
         <v>46</v>
       </c>
       <c r="B41" s="14">
-        <v>29.2216</v>
+        <v>29.3584</v>
       </c>
       <c r="C41" s="15">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="D41" s="16">
-        <v>1722587</v>
+        <v>1677345</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
@@ -1597,13 +1615,13 @@
         <v>47</v>
       </c>
       <c r="B42" s="14">
-        <v>28.1138</v>
+        <v>28.4531</v>
       </c>
       <c r="C42" s="15">
-        <v>-3.78</v>
+        <v>6.56</v>
       </c>
       <c r="D42" s="16">
-        <v>1598562</v>
+        <v>1676134</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1613,13 +1631,13 @@
         <v>48</v>
       </c>
       <c r="B43" s="14">
-        <v>29.217</v>
+        <v>26.7023</v>
       </c>
       <c r="C43" s="15">
-        <v>2.41</v>
+        <v>-5.03</v>
       </c>
       <c r="D43" s="16">
-        <v>1454774</v>
+        <v>1681792</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
@@ -1629,13 +1647,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="14">
-        <v>28.5297</v>
+        <v>28.1177</v>
       </c>
       <c r="C44" s="15">
-        <v>-0.92</v>
+        <v>-2.77</v>
       </c>
       <c r="D44" s="16">
-        <v>1416314</v>
+        <v>1680995</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
@@ -1645,13 +1663,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="14">
-        <v>28.7945</v>
+        <v>28.9179</v>
       </c>
       <c r="C45" s="15">
-        <v>2.3</v>
+        <v>-2.63</v>
       </c>
       <c r="D45" s="16">
-        <v>1410593</v>
+        <v>1651309</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -1661,13 +1679,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="14">
-        <v>28.1481</v>
+        <v>29.6987</v>
       </c>
       <c r="C46" s="15">
-        <v>9.55</v>
+        <v>1.63</v>
       </c>
       <c r="D46" s="16">
-        <v>1387780</v>
+        <v>1732322</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
@@ -1677,13 +1695,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="14">
-        <v>25.6943</v>
+        <v>29.2216</v>
       </c>
       <c r="C47" s="15">
-        <v>-3.92</v>
+        <v>3.94</v>
       </c>
       <c r="D47" s="16">
-        <v>1375352</v>
+        <v>1722587</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
@@ -1693,13 +1711,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="14">
-        <v>26.7429</v>
+        <v>28.1138</v>
       </c>
       <c r="C48" s="15">
-        <v>7.21</v>
+        <v>-3.78</v>
       </c>
       <c r="D48" s="16">
-        <v>1366161</v>
+        <v>1598562</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -1709,13 +1727,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="14">
-        <v>24.9445</v>
+        <v>29.217</v>
       </c>
       <c r="C49" s="15">
-        <v>7.66</v>
+        <v>2.41</v>
       </c>
       <c r="D49" s="16">
-        <v>1351135</v>
+        <v>1454774</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12"/>
@@ -1725,13 +1743,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="14">
-        <v>23.1704</v>
+        <v>28.5297</v>
       </c>
       <c r="C50" s="15">
-        <v>-6.41</v>
+        <v>-0.92</v>
       </c>
       <c r="D50" s="16">
-        <v>1375553</v>
+        <v>1416314</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -1741,13 +1759,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="14">
-        <v>24.7583</v>
+        <v>28.7945</v>
       </c>
       <c r="C51" s="15">
-        <v>-4.99</v>
+        <v>2.3</v>
       </c>
       <c r="D51" s="16">
-        <v>1384429</v>
+        <v>1410593</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -1757,13 +1775,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="14">
-        <v>26.0581</v>
+        <v>28.1481</v>
       </c>
       <c r="C52" s="15">
-        <v>8.95</v>
+        <v>9.55</v>
       </c>
       <c r="D52" s="16">
-        <v>1381585</v>
+        <v>1387780</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
@@ -1773,13 +1791,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="14">
-        <v>23.9169</v>
+        <v>25.6943</v>
       </c>
       <c r="C53" s="15">
-        <v>-8.57</v>
+        <v>-3.92</v>
       </c>
       <c r="D53" s="16">
-        <v>1371863</v>
+        <v>1375352</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -1789,13 +1807,13 @@
         <v>59</v>
       </c>
       <c r="B54" s="14">
-        <v>26.1594</v>
+        <v>26.7429</v>
       </c>
       <c r="C54" s="15">
-        <v>-0.12</v>
+        <v>7.21</v>
       </c>
       <c r="D54" s="16">
-        <v>1287343</v>
+        <v>1366161</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
@@ -1805,13 +1823,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="14">
-        <v>26.1909</v>
+        <v>24.9445</v>
       </c>
       <c r="C55" s="15">
-        <v>-1.72</v>
+        <v>7.66</v>
       </c>
       <c r="D55" s="16">
-        <v>1170403</v>
+        <v>1351135</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12"/>
@@ -1821,13 +1839,13 @@
         <v>61</v>
       </c>
       <c r="B56" s="14">
-        <v>26.6484</v>
+        <v>23.1704</v>
       </c>
       <c r="C56" s="15">
-        <v>0.76</v>
+        <v>-6.41</v>
       </c>
       <c r="D56" s="16">
-        <v>1143247</v>
+        <v>1375553</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -1837,13 +1855,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="14">
-        <v>26.4469</v>
+        <v>24.7583</v>
       </c>
       <c r="C57" s="15">
-        <v>-5.76</v>
+        <v>-4.99</v>
       </c>
       <c r="D57" s="16">
-        <v>1137079</v>
+        <v>1384429</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -1853,13 +1871,13 @@
         <v>63</v>
       </c>
       <c r="B58" s="14">
-        <v>28.0635</v>
+        <v>26.0581</v>
       </c>
       <c r="C58" s="15">
-        <v>-3.24</v>
+        <v>8.95</v>
       </c>
       <c r="D58" s="16">
-        <v>1141735</v>
+        <v>1381585</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12"/>
@@ -1869,13 +1887,13 @@
         <v>64</v>
       </c>
       <c r="B59" s="14">
-        <v>29.0019</v>
+        <v>23.9169</v>
       </c>
       <c r="C59" s="15">
-        <v>5.74</v>
+        <v>-8.57</v>
       </c>
       <c r="D59" s="16">
-        <v>1140149</v>
+        <v>1371863</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -1885,13 +1903,13 @@
         <v>65</v>
       </c>
       <c r="B60" s="14">
-        <v>27.4275</v>
+        <v>26.1594</v>
       </c>
       <c r="C60" s="15">
-        <v>-2.25</v>
+        <v>-0.12</v>
       </c>
       <c r="D60" s="16">
-        <v>1132208</v>
+        <v>1287343</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12"/>
@@ -1901,13 +1919,13 @@
         <v>66</v>
       </c>
       <c r="B61" s="14">
-        <v>28.0597</v>
+        <v>26.1909</v>
       </c>
       <c r="C61" s="15">
-        <v>3.46</v>
+        <v>-1.72</v>
       </c>
       <c r="D61" s="16">
-        <v>1147749</v>
+        <v>1170403</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12"/>
@@ -1917,13 +1935,13 @@
         <v>67</v>
       </c>
       <c r="B62" s="14">
-        <v>27.1204</v>
+        <v>26.6484</v>
       </c>
       <c r="C62" s="15">
-        <v>-2.46</v>
+        <v>0.76</v>
       </c>
       <c r="D62" s="16">
-        <v>1152596</v>
+        <v>1143247</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12"/>
@@ -1933,13 +1951,13 @@
         <v>68</v>
       </c>
       <c r="B63" s="14">
-        <v>27.803</v>
+        <v>26.4469</v>
       </c>
       <c r="C63" s="15">
-        <v>1.38</v>
+        <v>-5.76</v>
       </c>
       <c r="D63" s="16">
-        <v>1154198</v>
+        <v>1137079</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12"/>
@@ -1949,13 +1967,13 @@
         <v>69</v>
       </c>
       <c r="B64" s="14">
-        <v>27.4252</v>
+        <v>28.0635</v>
       </c>
       <c r="C64" s="15">
-        <v>2.14</v>
+        <v>-3.24</v>
       </c>
       <c r="D64" s="16">
-        <v>1150734</v>
+        <v>1141735</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
@@ -1965,13 +1983,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="14">
-        <v>26.8514</v>
+        <v>29.0019</v>
       </c>
       <c r="C65" s="15">
-        <v>0.99</v>
+        <v>5.74</v>
       </c>
       <c r="D65" s="16">
-        <v>1153800</v>
+        <v>1140149</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12"/>
@@ -1981,13 +1999,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="14">
-        <v>26.5879</v>
+        <v>27.4275</v>
       </c>
       <c r="C66" s="15">
-        <v>3.19</v>
+        <v>-2.25</v>
       </c>
       <c r="D66" s="16">
-        <v>1101557</v>
+        <v>1132208</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12"/>
@@ -1997,13 +2015,13 @@
         <v>72</v>
       </c>
       <c r="B67" s="14">
-        <v>25.7667</v>
+        <v>28.0597</v>
       </c>
       <c r="C67" s="15">
-        <v>3.09</v>
+        <v>3.46</v>
       </c>
       <c r="D67" s="16">
-        <v>1014341</v>
+        <v>1147749</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -2013,13 +2031,13 @@
         <v>73</v>
       </c>
       <c r="B68" s="14">
-        <v>24.9942</v>
+        <v>27.1204</v>
       </c>
       <c r="C68" s="15">
-        <v>6.62</v>
+        <v>-2.46</v>
       </c>
       <c r="D68" s="16">
-        <v>1008521</v>
+        <v>1152596</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -2029,13 +2047,13 @@
         <v>74</v>
       </c>
       <c r="B69" s="14">
-        <v>23.4425</v>
+        <v>27.803</v>
       </c>
       <c r="C69" s="15">
-        <v>4.78</v>
+        <v>1.38</v>
       </c>
       <c r="D69" s="16">
-        <v>996086</v>
+        <v>1154198</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
@@ -2045,13 +2063,13 @@
         <v>75</v>
       </c>
       <c r="B70" s="14">
-        <v>22.3735</v>
+        <v>27.4252</v>
       </c>
       <c r="C70" s="15">
-        <v>-2.49</v>
+        <v>2.14</v>
       </c>
       <c r="D70" s="16">
-        <v>936620</v>
+        <v>1150734</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
@@ -2061,13 +2079,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="14">
-        <v>22.9443</v>
+        <v>26.8514</v>
       </c>
       <c r="C71" s="15">
-        <v>0.46</v>
+        <v>0.99</v>
       </c>
       <c r="D71" s="16">
-        <v>943879</v>
+        <v>1153800</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -2077,13 +2095,13 @@
         <v>77</v>
       </c>
       <c r="B72" s="14">
-        <v>22.8391</v>
+        <v>26.5879</v>
       </c>
       <c r="C72" s="15">
-        <v>19.72</v>
+        <v>3.19</v>
       </c>
       <c r="D72" s="16">
-        <v>941803</v>
+        <v>1101557</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -2093,13 +2111,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="14">
-        <v>19.0775</v>
+        <v>25.7667</v>
       </c>
       <c r="C73" s="15">
-        <v>-5.12</v>
+        <v>3.09</v>
       </c>
       <c r="D73" s="16">
-        <v>955223</v>
+        <v>1014341</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
@@ -2109,13 +2127,13 @@
         <v>79</v>
       </c>
       <c r="B74" s="14">
-        <v>20.1067</v>
+        <v>24.9942</v>
       </c>
       <c r="C74" s="15">
-        <v>-2.83</v>
+        <v>6.62</v>
       </c>
       <c r="D74" s="16">
-        <v>964204</v>
+        <v>1008521</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
@@ -2125,13 +2143,13 @@
         <v>80</v>
       </c>
       <c r="B75" s="14">
-        <v>20.6927</v>
+        <v>23.4425</v>
       </c>
       <c r="C75" s="15">
-        <v>3.04</v>
+        <v>4.78</v>
       </c>
       <c r="D75" s="16">
-        <v>966711</v>
+        <v>996086</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12"/>
@@ -2141,13 +2159,13 @@
         <v>81</v>
       </c>
       <c r="B76" s="14">
-        <v>20.0818</v>
+        <v>22.3735</v>
       </c>
       <c r="C76" s="15">
-        <v>-2.08</v>
+        <v>-2.49</v>
       </c>
       <c r="D76" s="16">
-        <v>972275</v>
+        <v>936620</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
@@ -2157,13 +2175,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="14">
-        <v>20.5081</v>
+        <v>22.9443</v>
       </c>
       <c r="C77" s="15">
-        <v>5.22</v>
+        <v>0.46</v>
       </c>
       <c r="D77" s="16">
-        <v>969359</v>
+        <v>943879</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12"/>
@@ -2173,13 +2191,13 @@
         <v>83</v>
       </c>
       <c r="B78" s="14">
-        <v>19.4916</v>
+        <v>22.8391</v>
       </c>
       <c r="C78" s="15">
-        <v>3.37</v>
+        <v>19.72</v>
       </c>
       <c r="D78" s="16">
-        <v>931780</v>
+        <v>941803</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -2189,13 +2207,13 @@
         <v>84</v>
       </c>
       <c r="B79" s="14">
-        <v>18.8562</v>
+        <v>19.0775</v>
       </c>
       <c r="C79" s="15">
-        <v>4.26</v>
+        <v>-5.12</v>
       </c>
       <c r="D79" s="16">
-        <v>867387</v>
+        <v>955223</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12"/>
@@ -2205,13 +2223,13 @@
         <v>85</v>
       </c>
       <c r="B80" s="14">
-        <v>18.0866</v>
+        <v>20.1067</v>
       </c>
       <c r="C80" s="15">
-        <v>-17.9</v>
+        <v>-2.83</v>
       </c>
       <c r="D80" s="16">
-        <v>841914</v>
+        <v>964204</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12"/>
@@ -2221,13 +2239,13 @@
         <v>86</v>
       </c>
       <c r="B81" s="14">
-        <v>22.0299</v>
+        <v>20.6927</v>
       </c>
       <c r="C81" s="15">
-        <v>-8.09</v>
+        <v>3.04</v>
       </c>
       <c r="D81" s="16">
-        <v>857939</v>
+        <v>966711</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2237,13 +2255,13 @@
         <v>87</v>
       </c>
       <c r="B82" s="14">
-        <v>23.9688</v>
+        <v>20.0818</v>
       </c>
       <c r="C82" s="15">
-        <v>-3.01</v>
+        <v>-2.08</v>
       </c>
       <c r="D82" s="16">
-        <v>858061</v>
+        <v>972275</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12"/>
@@ -2253,13 +2271,13 @@
         <v>88</v>
       </c>
       <c r="B83" s="14">
-        <v>24.7119</v>
+        <v>20.5081</v>
       </c>
       <c r="C83" s="15">
-        <v>1.35</v>
+        <v>5.22</v>
       </c>
       <c r="D83" s="16">
-        <v>855605</v>
+        <v>969359</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12"/>
@@ -2269,13 +2287,13 @@
         <v>89</v>
       </c>
       <c r="B84" s="14">
-        <v>24.3826</v>
+        <v>19.4916</v>
       </c>
       <c r="C84" s="15">
-        <v>2.71</v>
+        <v>3.37</v>
       </c>
       <c r="D84" s="16">
-        <v>846151</v>
+        <v>931780</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12"/>
@@ -2285,13 +2303,13 @@
         <v>90</v>
       </c>
       <c r="B85" s="14">
-        <v>23.7392</v>
+        <v>18.8562</v>
       </c>
       <c r="C85" s="15">
-        <v>0.72</v>
+        <v>4.26</v>
       </c>
       <c r="D85" s="16">
-        <v>841907</v>
+        <v>867387</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="12"/>
@@ -2301,13 +2319,13 @@
         <v>91</v>
       </c>
       <c r="B86" s="14">
-        <v>23.5698</v>
+        <v>18.0866</v>
       </c>
       <c r="C86" s="15">
-        <v>3.73</v>
+        <v>-17.9</v>
       </c>
       <c r="D86" s="16">
-        <v>845465</v>
+        <v>841914</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12"/>
@@ -2317,13 +2335,13 @@
         <v>92</v>
       </c>
       <c r="B87" s="14">
-        <v>22.7222</v>
+        <v>22.0299</v>
       </c>
       <c r="C87" s="15">
-        <v>-1.07</v>
+        <v>-8.09</v>
       </c>
       <c r="D87" s="16">
-        <v>851371</v>
+        <v>857939</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2333,13 +2351,13 @@
         <v>93</v>
       </c>
       <c r="B88" s="14">
-        <v>22.9686</v>
+        <v>23.9688</v>
       </c>
       <c r="C88" s="15">
-        <v>-0.43</v>
+        <v>-3.01</v>
       </c>
       <c r="D88" s="16">
-        <v>854459</v>
+        <v>858061</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12"/>
@@ -2349,13 +2367,13 @@
         <v>94</v>
       </c>
       <c r="B89" s="14">
-        <v>23.0684</v>
+        <v>24.7119</v>
       </c>
       <c r="C89" s="15">
-        <v>6.75</v>
+        <v>1.35</v>
       </c>
       <c r="D89" s="16">
-        <v>847628</v>
+        <v>855605</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -2365,13 +2383,13 @@
         <v>95</v>
       </c>
       <c r="B90" s="14">
-        <v>21.6108</v>
+        <v>24.3826</v>
       </c>
       <c r="C90" s="15">
-        <v>-5.23</v>
+        <v>2.71</v>
       </c>
       <c r="D90" s="16">
-        <v>803441</v>
+        <v>846151</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -2381,13 +2399,13 @@
         <v>96</v>
       </c>
       <c r="B91" s="14">
-        <v>22.8026</v>
+        <v>23.7392</v>
       </c>
       <c r="C91" s="15">
-        <v>4.74</v>
+        <v>0.72</v>
       </c>
       <c r="D91" s="16">
-        <v>718935</v>
+        <v>841907</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -2397,13 +2415,13 @@
         <v>97</v>
       </c>
       <c r="B92" s="14">
-        <v>21.7712</v>
+        <v>23.5698</v>
       </c>
       <c r="C92" s="15">
-        <v>2.2</v>
+        <v>3.73</v>
       </c>
       <c r="D92" s="16">
-        <v>688109</v>
+        <v>845465</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -2413,13 +2431,13 @@
         <v>98</v>
       </c>
       <c r="B93" s="14">
-        <v>21.303</v>
+        <v>22.7222</v>
       </c>
       <c r="C93" s="15">
-        <v>5.38</v>
+        <v>-1.07</v>
       </c>
       <c r="D93" s="16">
-        <v>681469</v>
+        <v>851371</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -2429,13 +2447,13 @@
         <v>99</v>
       </c>
       <c r="B94" s="14">
-        <v>20.215</v>
+        <v>22.9686</v>
       </c>
       <c r="C94" s="15">
-        <v>5.2</v>
+        <v>-0.43</v>
       </c>
       <c r="D94" s="16">
-        <v>667101</v>
+        <v>854459</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12"/>
@@ -2445,13 +2463,13 @@
         <v>100</v>
       </c>
       <c r="B95" s="14">
-        <v>19.2165</v>
+        <v>23.0684</v>
       </c>
       <c r="C95" s="15">
-        <v>-5.94</v>
+        <v>6.75</v>
       </c>
       <c r="D95" s="16">
-        <v>667383</v>
+        <v>847628</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
@@ -2461,13 +2479,13 @@
         <v>101</v>
       </c>
       <c r="B96" s="14">
-        <v>20.4298</v>
+        <v>21.6108</v>
       </c>
       <c r="C96" s="15">
-        <v>-1.76</v>
+        <v>-5.23</v>
       </c>
       <c r="D96" s="16">
-        <v>669111</v>
+        <v>803441</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
@@ -2477,13 +2495,13 @@
         <v>102</v>
       </c>
       <c r="B97" s="14">
-        <v>20.7954</v>
+        <v>22.8026</v>
       </c>
       <c r="C97" s="15">
-        <v>-6.97</v>
+        <v>4.74</v>
       </c>
       <c r="D97" s="16">
-        <v>665867</v>
+        <v>718935</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -2493,13 +2511,13 @@
         <v>103</v>
       </c>
       <c r="B98" s="14">
-        <v>22.3534</v>
+        <v>21.7712</v>
       </c>
       <c r="C98" s="15">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="D98" s="16">
-        <v>665362</v>
+        <v>688109</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -2509,13 +2527,13 @@
         <v>104</v>
       </c>
       <c r="B99" s="14">
-        <v>22.006</v>
+        <v>21.303</v>
       </c>
       <c r="C99" s="15">
-        <v>-2.1</v>
+        <v>5.38</v>
       </c>
       <c r="D99" s="16">
-        <v>664905</v>
+        <v>681469</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -2525,13 +2543,13 @@
         <v>105</v>
       </c>
       <c r="B100" s="14">
-        <v>22.4772</v>
+        <v>20.215</v>
       </c>
       <c r="C100" s="15">
-        <v>3.04</v>
+        <v>5.2</v>
       </c>
       <c r="D100" s="16">
-        <v>666304</v>
+        <v>667101</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -2541,13 +2559,13 @@
         <v>106</v>
       </c>
       <c r="B101" s="14">
-        <v>21.8133</v>
+        <v>19.2165</v>
       </c>
       <c r="C101" s="15">
-        <v>-0.8</v>
+        <v>-5.94</v>
       </c>
       <c r="D101" s="16">
-        <v>649857</v>
+        <v>667383</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
@@ -2557,13 +2575,13 @@
         <v>107</v>
       </c>
       <c r="B102" s="14">
-        <v>21.9894</v>
+        <v>20.4298</v>
       </c>
       <c r="C102" s="15">
-        <v>-0.4</v>
+        <v>-1.76</v>
       </c>
       <c r="D102" s="16">
-        <v>644418</v>
+        <v>669111</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12"/>
@@ -2573,13 +2591,13 @@
         <v>108</v>
       </c>
       <c r="B103" s="14">
-        <v>22.0767</v>
+        <v>20.7954</v>
       </c>
       <c r="C103" s="15">
-        <v>6.38</v>
+        <v>-6.97</v>
       </c>
       <c r="D103" s="16">
-        <v>604788</v>
+        <v>665867</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -2589,13 +2607,13 @@
         <v>109</v>
       </c>
       <c r="B104" s="14">
-        <v>20.752</v>
+        <v>22.3534</v>
       </c>
       <c r="C104" s="15">
-        <v>-2.44</v>
+        <v>1.58</v>
       </c>
       <c r="D104" s="16">
-        <v>593084</v>
+        <v>665362</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12"/>
@@ -2605,13 +2623,13 @@
         <v>110</v>
       </c>
       <c r="B105" s="14">
-        <v>21.2709</v>
+        <v>22.006</v>
       </c>
       <c r="C105" s="15">
-        <v>-2.82</v>
+        <v>-2.1</v>
       </c>
       <c r="D105" s="16">
-        <v>583239</v>
+        <v>664905</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -2621,13 +2639,13 @@
         <v>111</v>
       </c>
       <c r="B106" s="14">
-        <v>21.889</v>
+        <v>22.4772</v>
       </c>
       <c r="C106" s="15">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="D106" s="16">
-        <v>575763</v>
+        <v>666304</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="12"/>
@@ -2637,13 +2655,13 @@
         <v>112</v>
       </c>
       <c r="B107" s="14">
-        <v>21.2419</v>
+        <v>21.8133</v>
       </c>
       <c r="C107" s="15">
-        <v>-1.14</v>
+        <v>-0.8</v>
       </c>
       <c r="D107" s="16">
-        <v>556044</v>
+        <v>649857</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="12"/>
@@ -2653,13 +2671,13 @@
         <v>113</v>
       </c>
       <c r="B108" s="14">
-        <v>21.4864</v>
+        <v>21.9894</v>
       </c>
       <c r="C108" s="15">
-        <v>-2.49</v>
+        <v>-0.4</v>
       </c>
       <c r="D108" s="16">
-        <v>543886</v>
+        <v>644418</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
@@ -2669,13 +2687,13 @@
         <v>114</v>
       </c>
       <c r="B109" s="14">
-        <v>22.0356</v>
+        <v>22.0767</v>
       </c>
       <c r="C109" s="15">
-        <v>2.6</v>
+        <v>6.38</v>
       </c>
       <c r="D109" s="16">
-        <v>536700</v>
+        <v>604788</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="12"/>
@@ -2685,13 +2703,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="14">
-        <v>21.478</v>
+        <v>20.752</v>
       </c>
       <c r="C110" s="15">
-        <v>4.69</v>
+        <v>-2.44</v>
       </c>
       <c r="D110" s="16">
-        <v>525076</v>
+        <v>593084</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
@@ -2701,13 +2719,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="14">
-        <v>20.5167</v>
+        <v>21.2709</v>
       </c>
       <c r="C111" s="15">
-        <v>-0.41</v>
+        <v>-2.82</v>
       </c>
       <c r="D111" s="16">
-        <v>517170</v>
+        <v>583239</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="12"/>
@@ -2717,13 +2735,13 @@
         <v>117</v>
       </c>
       <c r="B112" s="14">
-        <v>20.6018</v>
+        <v>21.889</v>
       </c>
       <c r="C112" s="15">
-        <v>-0.41</v>
+        <v>3.05</v>
       </c>
       <c r="D112" s="16">
-        <v>516385</v>
+        <v>575763</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="12"/>
@@ -2733,13 +2751,13 @@
         <v>118</v>
       </c>
       <c r="B113" s="14">
-        <v>20.6865</v>
+        <v>21.2419</v>
       </c>
       <c r="C113" s="15">
-        <v>-2.72</v>
+        <v>-1.14</v>
       </c>
       <c r="D113" s="16">
-        <v>515324</v>
+        <v>556044</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="12"/>
@@ -2749,13 +2767,13 @@
         <v>119</v>
       </c>
       <c r="B114" s="14">
-        <v>21.2641</v>
+        <v>21.4864</v>
       </c>
       <c r="C114" s="15">
-        <v>1.87</v>
+        <v>-2.49</v>
       </c>
       <c r="D114" s="16">
-        <v>494739</v>
+        <v>543886</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
@@ -2765,13 +2783,13 @@
         <v>120</v>
       </c>
       <c r="B115" s="14">
-        <v>20.8729</v>
+        <v>22.0356</v>
       </c>
       <c r="C115" s="15">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="D115" s="16">
-        <v>449488</v>
+        <v>536700</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -2781,13 +2799,13 @@
         <v>121</v>
       </c>
       <c r="B116" s="14">
-        <v>20.2105</v>
+        <v>21.478</v>
       </c>
       <c r="C116" s="15">
-        <v>5.39</v>
+        <v>4.69</v>
       </c>
       <c r="D116" s="16">
-        <v>439668</v>
+        <v>525076</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="12"/>
@@ -2797,13 +2815,13 @@
         <v>122</v>
       </c>
       <c r="B117" s="14">
-        <v>19.1772</v>
+        <v>20.5167</v>
       </c>
       <c r="C117" s="15">
-        <v>2.19</v>
+        <v>-0.41</v>
       </c>
       <c r="D117" s="16">
-        <v>431165</v>
+        <v>517170</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="12"/>
@@ -2813,13 +2831,13 @@
         <v>123</v>
       </c>
       <c r="B118" s="14">
-        <v>18.7654</v>
+        <v>20.6018</v>
       </c>
       <c r="C118" s="15">
-        <v>-2.24</v>
+        <v>-0.41</v>
       </c>
       <c r="D118" s="16">
-        <v>422201</v>
+        <v>516385</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="12"/>
@@ -2829,13 +2847,13 @@
         <v>124</v>
       </c>
       <c r="B119" s="14">
-        <v>19.1954</v>
+        <v>20.6865</v>
       </c>
       <c r="C119" s="15">
-        <v>6.55</v>
+        <v>-2.72</v>
       </c>
       <c r="D119" s="16">
-        <v>425382</v>
+        <v>515324</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="12"/>
@@ -2845,13 +2863,13 @@
         <v>125</v>
       </c>
       <c r="B120" s="14">
-        <v>18.0154</v>
+        <v>21.2641</v>
       </c>
       <c r="C120" s="15">
-        <v>0.93</v>
+        <v>1.87</v>
       </c>
       <c r="D120" s="16">
-        <v>421039</v>
+        <v>494739</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="12"/>
@@ -2861,13 +2879,13 @@
         <v>126</v>
       </c>
       <c r="B121" s="14">
-        <v>17.849</v>
+        <v>20.8729</v>
       </c>
       <c r="C121" s="15">
-        <v>1.31</v>
+        <v>3.28</v>
       </c>
       <c r="D121" s="16">
-        <v>425552</v>
+        <v>449488</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="12"/>
@@ -2877,13 +2895,13 @@
         <v>127</v>
       </c>
       <c r="B122" s="14">
-        <v>17.6184</v>
+        <v>20.2105</v>
       </c>
       <c r="C122" s="15">
-        <v>-0.34</v>
+        <v>5.39</v>
       </c>
       <c r="D122" s="16">
-        <v>429235</v>
+        <v>439668</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="12"/>
@@ -2893,13 +2911,13 @@
         <v>128</v>
       </c>
       <c r="B123" s="14">
-        <v>17.6784</v>
+        <v>19.1772</v>
       </c>
       <c r="C123" s="15">
-        <v>-0.02</v>
+        <v>2.19</v>
       </c>
       <c r="D123" s="16">
-        <v>431025</v>
+        <v>431165</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="12"/>
@@ -2909,13 +2927,13 @@
         <v>129</v>
       </c>
       <c r="B124" s="14">
-        <v>17.6823</v>
+        <v>18.7654</v>
       </c>
       <c r="C124" s="15">
-        <v>4.21</v>
+        <v>-2.24</v>
       </c>
       <c r="D124" s="16">
-        <v>427073</v>
+        <v>422201</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
@@ -2925,13 +2943,13 @@
         <v>130</v>
       </c>
       <c r="B125" s="14">
-        <v>16.9676</v>
+        <v>19.1954</v>
       </c>
       <c r="C125" s="15">
-        <v>-5.59</v>
+        <v>6.55</v>
       </c>
       <c r="D125" s="16">
-        <v>423611</v>
+        <v>425382</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -2941,13 +2959,13 @@
         <v>131</v>
       </c>
       <c r="B126" s="14">
-        <v>17.9726</v>
+        <v>18.0154</v>
       </c>
       <c r="C126" s="15">
-        <v>3.29</v>
+        <v>0.93</v>
       </c>
       <c r="D126" s="16">
-        <v>406589</v>
+        <v>421039</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
@@ -2957,13 +2975,13 @@
         <v>132</v>
       </c>
       <c r="B127" s="14">
-        <v>17.401</v>
+        <v>17.849</v>
       </c>
       <c r="C127" s="15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="D127" s="16">
-        <v>383668</v>
+        <v>425552</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="12"/>
@@ -2973,13 +2991,13 @@
         <v>133</v>
       </c>
       <c r="B128" s="14">
-        <v>17.1786</v>
+        <v>17.6184</v>
       </c>
       <c r="C128" s="15">
-        <v>0.93</v>
+        <v>-0.34</v>
       </c>
       <c r="D128" s="16">
-        <v>383404</v>
+        <v>429235</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12"/>
@@ -2989,13 +3007,13 @@
         <v>134</v>
       </c>
       <c r="B129" s="14">
-        <v>17.0211</v>
+        <v>17.6784</v>
       </c>
       <c r="C129" s="15">
-        <v>-1.23</v>
+        <v>-0.02</v>
       </c>
       <c r="D129" s="16">
-        <v>369347</v>
+        <v>431025</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="12"/>
@@ -3005,13 +3023,13 @@
         <v>135</v>
       </c>
       <c r="B130" s="14">
-        <v>17.2327</v>
+        <v>17.6823</v>
       </c>
       <c r="C130" s="15">
-        <v>-4.57</v>
+        <v>4.21</v>
       </c>
       <c r="D130" s="16">
-        <v>365521</v>
+        <v>427073</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
@@ -3021,13 +3039,13 @@
         <v>136</v>
       </c>
       <c r="B131" s="14">
-        <v>18.0587</v>
+        <v>16.9676</v>
       </c>
       <c r="C131" s="15">
-        <v>-5.97</v>
+        <v>-5.59</v>
       </c>
       <c r="D131" s="16">
-        <v>351951</v>
+        <v>423611</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12"/>
@@ -3037,13 +3055,13 @@
         <v>137</v>
       </c>
       <c r="B132" s="14">
-        <v>19.2059</v>
+        <v>17.9726</v>
       </c>
       <c r="C132" s="15">
-        <v>1.7</v>
+        <v>3.29</v>
       </c>
       <c r="D132" s="16">
-        <v>329812</v>
+        <v>406589</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="12"/>
@@ -3053,13 +3071,13 @@
         <v>138</v>
       </c>
       <c r="B133" s="14">
-        <v>18.8858</v>
+        <v>17.401</v>
       </c>
       <c r="C133" s="15">
-        <v>9.54</v>
+        <v>1.3</v>
       </c>
       <c r="D133" s="16">
-        <v>332262</v>
+        <v>383668</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
@@ -3069,13 +3087,13 @@
         <v>139</v>
       </c>
       <c r="B134" s="14">
-        <v>17.2404</v>
+        <v>17.1786</v>
       </c>
       <c r="C134" s="15">
-        <v>-4.1</v>
+        <v>0.93</v>
       </c>
       <c r="D134" s="16">
-        <v>334394</v>
+        <v>383404</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="12"/>
@@ -3085,13 +3103,13 @@
         <v>140</v>
       </c>
       <c r="B135" s="14">
-        <v>17.9771</v>
+        <v>17.0211</v>
       </c>
       <c r="C135" s="15">
-        <v>-7.71</v>
+        <v>-1.23</v>
       </c>
       <c r="D135" s="16">
-        <v>334775</v>
+        <v>369347</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="12"/>
@@ -3101,13 +3119,13 @@
         <v>141</v>
       </c>
       <c r="B136" s="14">
-        <v>19.4794</v>
+        <v>17.2327</v>
       </c>
       <c r="C136" s="15">
-        <v>5.85</v>
+        <v>-4.57</v>
       </c>
       <c r="D136" s="16">
-        <v>331859</v>
+        <v>365521</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="12"/>
@@ -3117,13 +3135,13 @@
         <v>142</v>
       </c>
       <c r="B137" s="14">
-        <v>18.4037</v>
+        <v>18.0587</v>
       </c>
       <c r="C137" s="15">
-        <v>-3.92</v>
+        <v>-5.97</v>
       </c>
       <c r="D137" s="16">
-        <v>331398</v>
+        <v>351951</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="12"/>
@@ -3133,13 +3151,13 @@
         <v>143</v>
       </c>
       <c r="B138" s="14">
-        <v>19.1537</v>
+        <v>19.2059</v>
       </c>
       <c r="C138" s="15">
-        <v>0.67</v>
+        <v>1.7</v>
       </c>
       <c r="D138" s="16">
-        <v>324977</v>
+        <v>329812</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="12"/>
@@ -3149,13 +3167,13 @@
         <v>144</v>
       </c>
       <c r="B139" s="14">
-        <v>19.0263</v>
+        <v>18.8858</v>
       </c>
       <c r="C139" s="15">
-        <v>0.89</v>
+        <v>9.54</v>
       </c>
       <c r="D139" s="16">
-        <v>317273</v>
+        <v>332262</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="12"/>
@@ -3165,13 +3183,13 @@
         <v>145</v>
       </c>
       <c r="B140" s="14">
-        <v>18.8585</v>
+        <v>17.2404</v>
       </c>
       <c r="C140" s="15">
-        <v>1.95</v>
+        <v>-4.1</v>
       </c>
       <c r="D140" s="16">
-        <v>315938</v>
+        <v>334394</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="12"/>
@@ -3181,13 +3199,13 @@
         <v>146</v>
       </c>
       <c r="B141" s="14">
-        <v>18.4986</v>
+        <v>17.9771</v>
       </c>
       <c r="C141" s="15">
-        <v>7.39</v>
+        <v>-7.71</v>
       </c>
       <c r="D141" s="16">
-        <v>321090</v>
+        <v>334775</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12"/>
@@ -3197,13 +3215,13 @@
         <v>147</v>
       </c>
       <c r="B142" s="14">
-        <v>17.2265</v>
+        <v>19.4794</v>
       </c>
       <c r="C142" s="15">
-        <v>7.47</v>
+        <v>5.85</v>
       </c>
       <c r="D142" s="16">
-        <v>313313</v>
+        <v>331859</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="12"/>
@@ -3213,13 +3231,13 @@
         <v>148</v>
       </c>
       <c r="B143" s="14">
-        <v>16.0299</v>
+        <v>18.4037</v>
       </c>
       <c r="C143" s="15">
-        <v>-2.26</v>
+        <v>-3.92</v>
       </c>
       <c r="D143" s="16">
-        <v>307702</v>
+        <v>331398</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="12"/>
@@ -3229,13 +3247,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="14">
-        <v>16.4006</v>
+        <v>19.1537</v>
       </c>
       <c r="C144" s="15">
-        <v>4.09</v>
+        <v>0.67</v>
       </c>
       <c r="D144" s="16">
-        <v>314807</v>
+        <v>324977</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="12"/>
@@ -3245,13 +3263,13 @@
         <v>150</v>
       </c>
       <c r="B145" s="14">
-        <v>15.7564</v>
+        <v>19.0263</v>
       </c>
       <c r="C145" s="15">
-        <v>-3.91</v>
+        <v>0.89</v>
       </c>
       <c r="D145" s="16">
-        <v>313983</v>
+        <v>317273</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="12"/>
@@ -3261,13 +3279,13 @@
         <v>151</v>
       </c>
       <c r="B146" s="14">
-        <v>16.3969</v>
+        <v>18.8585</v>
       </c>
       <c r="C146" s="15">
-        <v>0.58</v>
+        <v>1.95</v>
       </c>
       <c r="D146" s="16">
-        <v>317840</v>
+        <v>315938</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="12"/>
@@ -3277,13 +3295,13 @@
         <v>152</v>
       </c>
       <c r="B147" s="14">
-        <v>16.3023</v>
+        <v>18.4986</v>
       </c>
       <c r="C147" s="15">
-        <v>1.99</v>
+        <v>7.39</v>
       </c>
       <c r="D147" s="16">
-        <v>319776</v>
+        <v>321090</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12"/>
@@ -3293,13 +3311,13 @@
         <v>153</v>
       </c>
       <c r="B148" s="14">
-        <v>15.9839</v>
+        <v>17.2265</v>
       </c>
       <c r="C148" s="15">
-        <v>-3.62</v>
+        <v>7.47</v>
       </c>
       <c r="D148" s="16">
-        <v>326712</v>
+        <v>313313</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="12"/>
@@ -3309,13 +3327,13 @@
         <v>154</v>
       </c>
       <c r="B149" s="14">
-        <v>16.585</v>
+        <v>16.0299</v>
       </c>
       <c r="C149" s="15">
-        <v>-1.81</v>
+        <v>-2.26</v>
       </c>
       <c r="D149" s="16">
-        <v>326835</v>
+        <v>307702</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="12"/>
@@ -3325,13 +3343,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="14">
-        <v>16.89</v>
+        <v>16.4006</v>
       </c>
       <c r="C150" s="15">
-        <v>2.12</v>
+        <v>4.09</v>
       </c>
       <c r="D150" s="16">
-        <v>316759</v>
+        <v>314807</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="12"/>
@@ -3341,13 +3359,13 @@
         <v>156</v>
       </c>
       <c r="B151" s="14">
-        <v>16.5388</v>
+        <v>15.7564</v>
       </c>
       <c r="C151" s="15">
-        <v>2</v>
+        <v>-3.91</v>
       </c>
       <c r="D151" s="16">
-        <v>311960</v>
+        <v>313983</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="12"/>
@@ -3357,13 +3375,13 @@
         <v>157</v>
       </c>
       <c r="B152" s="14">
-        <v>16.2147</v>
+        <v>16.3969</v>
       </c>
       <c r="C152" s="15">
-        <v>0.02</v>
+        <v>0.58</v>
       </c>
       <c r="D152" s="16">
-        <v>299481</v>
+        <v>317840</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="12"/>
@@ -3373,13 +3391,13 @@
         <v>158</v>
       </c>
       <c r="B153" s="14">
-        <v>16.212</v>
+        <v>16.3023</v>
       </c>
       <c r="C153" s="15">
-        <v>5.71</v>
+        <v>1.99</v>
       </c>
       <c r="D153" s="16">
-        <v>299583</v>
+        <v>319776</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="12"/>
@@ -3389,13 +3407,13 @@
         <v>159</v>
       </c>
       <c r="B154" s="14">
-        <v>15.336</v>
+        <v>15.9839</v>
       </c>
       <c r="C154" s="15">
-        <v>-2.61</v>
+        <v>-3.62</v>
       </c>
       <c r="D154" s="16">
-        <v>295466</v>
+        <v>326712</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="12"/>
@@ -3405,13 +3423,13 @@
         <v>160</v>
       </c>
       <c r="B155" s="14">
-        <v>15.7463</v>
+        <v>16.585</v>
       </c>
       <c r="C155" s="15">
-        <v>0.38</v>
+        <v>-1.81</v>
       </c>
       <c r="D155" s="16">
-        <v>296547</v>
+        <v>326835</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="12"/>
@@ -3421,13 +3439,13 @@
         <v>161</v>
       </c>
       <c r="B156" s="14">
-        <v>15.6861</v>
+        <v>16.89</v>
       </c>
       <c r="C156" s="15">
-        <v>0.54</v>
+        <v>2.12</v>
       </c>
       <c r="D156" s="16">
-        <v>292185</v>
+        <v>316759</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="12"/>
@@ -3437,13 +3455,13 @@
         <v>162</v>
       </c>
       <c r="B157" s="14">
-        <v>15.6022</v>
+        <v>16.5388</v>
       </c>
       <c r="C157" s="15">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="D157" s="16">
-        <v>291815</v>
+        <v>311960</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="12"/>
@@ -3453,13 +3471,13 @@
         <v>163</v>
       </c>
       <c r="B158" s="14">
-        <v>15.0304</v>
+        <v>16.2147</v>
       </c>
       <c r="C158" s="15">
-        <v>5.47</v>
+        <v>0.02</v>
       </c>
       <c r="D158" s="16">
-        <v>287293</v>
+        <v>299481</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="12"/>
@@ -3469,13 +3487,13 @@
         <v>164</v>
       </c>
       <c r="B159" s="14">
-        <v>14.2508</v>
+        <v>16.212</v>
       </c>
       <c r="C159" s="15">
-        <v>-1.6</v>
+        <v>5.71</v>
       </c>
       <c r="D159" s="16">
-        <v>285409</v>
+        <v>299583</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="12"/>
@@ -3485,13 +3503,13 @@
         <v>165</v>
       </c>
       <c r="B160" s="14">
-        <v>14.4826</v>
+        <v>15.336</v>
       </c>
       <c r="C160" s="15">
-        <v>6.81</v>
+        <v>-2.61</v>
       </c>
       <c r="D160" s="16">
-        <v>288332</v>
+        <v>295466</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="12"/>
@@ -3501,13 +3519,13 @@
         <v>166</v>
       </c>
       <c r="B161" s="14">
-        <v>13.5591</v>
+        <v>15.7463</v>
       </c>
       <c r="C161" s="15">
-        <v>-4.69</v>
+        <v>0.38</v>
       </c>
       <c r="D161" s="16">
-        <v>294120</v>
+        <v>296547</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="12"/>
@@ -3517,13 +3535,13 @@
         <v>167</v>
       </c>
       <c r="B162" s="14">
-        <v>14.2262</v>
+        <v>15.6861</v>
       </c>
       <c r="C162" s="15">
-        <v>4.31</v>
+        <v>0.54</v>
       </c>
       <c r="D162" s="16">
-        <v>277446</v>
+        <v>292185</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="12"/>
@@ -3533,13 +3551,13 @@
         <v>168</v>
       </c>
       <c r="B163" s="14">
-        <v>13.6383</v>
+        <v>15.6022</v>
       </c>
       <c r="C163" s="15">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="D163" s="16">
-        <v>273642</v>
+        <v>291815</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="12"/>
@@ -3549,13 +3567,13 @@
         <v>169</v>
       </c>
       <c r="B164" s="14">
-        <v>13.2675</v>
+        <v>15.0304</v>
       </c>
       <c r="C164" s="15">
-        <v>-0.49</v>
+        <v>5.47</v>
       </c>
       <c r="D164" s="16">
-        <v>273311</v>
+        <v>287293</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="12"/>
@@ -3565,13 +3583,13 @@
         <v>170</v>
       </c>
       <c r="B165" s="14">
-        <v>13.3332</v>
+        <v>14.2508</v>
       </c>
       <c r="C165" s="15">
-        <v>0.41</v>
+        <v>-1.6</v>
       </c>
       <c r="D165" s="16">
-        <v>269139</v>
+        <v>285409</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="12"/>
@@ -3581,13 +3599,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="14">
-        <v>13.2786</v>
+        <v>14.4826</v>
       </c>
       <c r="C166" s="15">
-        <v>2.66</v>
+        <v>6.81</v>
       </c>
       <c r="D166" s="16">
-        <v>263037</v>
+        <v>288332</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="12"/>
@@ -3597,13 +3615,13 @@
         <v>172</v>
       </c>
       <c r="B167" s="14">
-        <v>12.9342</v>
+        <v>13.5591</v>
       </c>
       <c r="C167" s="15">
-        <v>2.04</v>
+        <v>-4.69</v>
       </c>
       <c r="D167" s="16">
-        <v>198754</v>
+        <v>294120</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="12"/>
@@ -3613,13 +3631,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="14">
-        <v>12.6757</v>
+        <v>14.2262</v>
       </c>
       <c r="C168" s="15">
-        <v>3.87</v>
+        <v>4.31</v>
       </c>
       <c r="D168" s="16">
-        <v>199980</v>
+        <v>277446</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="12"/>
@@ -3629,13 +3647,13 @@
         <v>174</v>
       </c>
       <c r="B169" s="14">
-        <v>12.204</v>
+        <v>13.6383</v>
       </c>
       <c r="C169" s="15">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="D169" s="16">
-        <v>200970</v>
+        <v>273642</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="12"/>
@@ -3645,13 +3663,13 @@
         <v>175</v>
       </c>
       <c r="B170" s="14">
-        <v>12.0241</v>
+        <v>13.2675</v>
       </c>
       <c r="C170" s="15">
-        <v>-1.24</v>
+        <v>-0.49</v>
       </c>
       <c r="D170" s="16">
-        <v>202101</v>
+        <v>273311</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="12"/>
@@ -3661,13 +3679,13 @@
         <v>176</v>
       </c>
       <c r="B171" s="14">
-        <v>12.1748</v>
+        <v>13.3332</v>
       </c>
       <c r="C171" s="15">
-        <v>3.88</v>
+        <v>0.41</v>
       </c>
       <c r="D171" s="16">
-        <v>198314</v>
+        <v>269139</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="12"/>
@@ -3677,13 +3695,13 @@
         <v>177</v>
       </c>
       <c r="B172" s="14">
-        <v>11.7197</v>
+        <v>13.2786</v>
       </c>
       <c r="C172" s="15">
         <v>2.66</v>
       </c>
       <c r="D172" s="16">
-        <v>200713</v>
+        <v>263037</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="12"/>
@@ -3693,13 +3711,13 @@
         <v>178</v>
       </c>
       <c r="B173" s="14">
-        <v>11.416</v>
+        <v>12.9342</v>
       </c>
       <c r="C173" s="15">
-        <v>5.97</v>
+        <v>2.04</v>
       </c>
       <c r="D173" s="16">
-        <v>213425</v>
+        <v>198754</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="12"/>
@@ -3709,13 +3727,13 @@
         <v>179</v>
       </c>
       <c r="B174" s="14">
-        <v>10.7726</v>
+        <v>12.6757</v>
       </c>
       <c r="C174" s="15">
-        <v>-4.57</v>
+        <v>3.87</v>
       </c>
       <c r="D174" s="16">
-        <v>210390</v>
+        <v>199980</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="12"/>
@@ -3725,13 +3743,13 @@
         <v>180</v>
       </c>
       <c r="B175" s="14">
-        <v>11.2888</v>
+        <v>12.204</v>
       </c>
       <c r="C175" s="15">
-        <v>-4.75</v>
+        <v>1.5</v>
       </c>
       <c r="D175" s="16">
-        <v>206365</v>
+        <v>200970</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="12"/>
@@ -3741,13 +3759,13 @@
         <v>181</v>
       </c>
       <c r="B176" s="14">
-        <v>11.852</v>
+        <v>12.0241</v>
       </c>
       <c r="C176" s="15">
-        <v>-0.58</v>
+        <v>-1.24</v>
       </c>
       <c r="D176" s="16">
-        <v>157507</v>
+        <v>202101</v>
       </c>
       <c r="E176" s="12"/>
       <c r="F176" s="12"/>
@@ -3757,13 +3775,13 @@
         <v>182</v>
       </c>
       <c r="B177" s="14">
-        <v>11.9208</v>
+        <v>12.1748</v>
       </c>
       <c r="C177" s="15">
-        <v>4.82</v>
+        <v>3.88</v>
       </c>
       <c r="D177" s="16">
-        <v>160205</v>
+        <v>198314</v>
       </c>
       <c r="E177" s="12"/>
       <c r="F177" s="12"/>
@@ -3773,13 +3791,13 @@
         <v>183</v>
       </c>
       <c r="B178" s="14">
-        <v>11.3722</v>
+        <v>11.7197</v>
       </c>
       <c r="C178" s="15">
-        <v>3.79</v>
+        <v>2.66</v>
       </c>
       <c r="D178" s="16">
-        <v>150268</v>
+        <v>200713</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
@@ -3789,13 +3807,13 @@
         <v>184</v>
       </c>
       <c r="B179" s="14">
-        <v>10.9572</v>
+        <v>11.416</v>
       </c>
       <c r="C179" s="15">
-        <v>0.42</v>
+        <v>5.97</v>
       </c>
       <c r="D179" s="16">
-        <v>153441</v>
+        <v>213425</v>
       </c>
       <c r="E179" s="12"/>
       <c r="F179" s="12"/>
@@ -3805,13 +3823,13 @@
         <v>185</v>
       </c>
       <c r="B180" s="14">
-        <v>10.9114</v>
+        <v>10.7726</v>
       </c>
       <c r="C180" s="15">
-        <v>-2.66</v>
+        <v>-4.57</v>
       </c>
       <c r="D180" s="16">
-        <v>151631</v>
+        <v>210390</v>
       </c>
       <c r="E180" s="12"/>
       <c r="F180" s="12"/>
@@ -3821,13 +3839,13 @@
         <v>186</v>
       </c>
       <c r="B181" s="14">
-        <v>11.2095</v>
+        <v>11.2888</v>
       </c>
       <c r="C181" s="15">
-        <v>8.56</v>
+        <v>-4.75</v>
       </c>
       <c r="D181" s="16">
-        <v>142871</v>
+        <v>206365</v>
       </c>
       <c r="E181" s="12"/>
       <c r="F181" s="12"/>
@@ -3837,13 +3855,13 @@
         <v>187</v>
       </c>
       <c r="B182" s="14">
-        <v>10.3257</v>
+        <v>11.852</v>
       </c>
       <c r="C182" s="15">
-        <v>-8.54</v>
+        <v>-0.58</v>
       </c>
       <c r="D182" s="16">
-        <v>141565</v>
+        <v>157507</v>
       </c>
       <c r="E182" s="12"/>
       <c r="F182" s="12"/>
@@ -3853,13 +3871,13 @@
         <v>188</v>
       </c>
       <c r="B183" s="14">
-        <v>11.2894</v>
+        <v>11.9208</v>
       </c>
       <c r="C183" s="15">
-        <v>-10.9</v>
+        <v>4.82</v>
       </c>
       <c r="D183" s="16">
-        <v>141871</v>
+        <v>160205</v>
       </c>
       <c r="E183" s="12"/>
       <c r="F183" s="12"/>
@@ -3869,13 +3887,13 @@
         <v>189</v>
       </c>
       <c r="B184" s="14">
-        <v>12.6702</v>
+        <v>11.3722</v>
       </c>
       <c r="C184" s="15">
-        <v>-6.98</v>
+        <v>3.79</v>
       </c>
       <c r="D184" s="16">
-        <v>139960</v>
+        <v>150268</v>
       </c>
       <c r="E184" s="12"/>
       <c r="F184" s="12"/>
@@ -3885,13 +3903,13 @@
         <v>190</v>
       </c>
       <c r="B185" s="14">
-        <v>13.6202</v>
+        <v>10.9572</v>
       </c>
       <c r="C185" s="15">
-        <v>-0.31</v>
+        <v>0.42</v>
       </c>
       <c r="D185" s="16">
-        <v>139096</v>
+        <v>153441</v>
       </c>
       <c r="E185" s="12"/>
       <c r="F185" s="12"/>
@@ -3901,13 +3919,13 @@
         <v>191</v>
       </c>
       <c r="B186" s="14">
-        <v>13.662</v>
+        <v>10.9114</v>
       </c>
       <c r="C186" s="15">
-        <v>-0.77</v>
+        <v>-2.66</v>
       </c>
       <c r="D186" s="16">
-        <v>135452</v>
+        <v>151631</v>
       </c>
       <c r="E186" s="12"/>
       <c r="F186" s="12"/>
@@ -3917,13 +3935,13 @@
         <v>192</v>
       </c>
       <c r="B187" s="14">
-        <v>13.7682</v>
+        <v>11.2095</v>
       </c>
       <c r="C187" s="15">
-        <v>3.05</v>
+        <v>8.56</v>
       </c>
       <c r="D187" s="16">
-        <v>131534</v>
+        <v>142871</v>
       </c>
       <c r="E187" s="12"/>
       <c r="F187" s="12"/>
@@ -3933,13 +3951,13 @@
         <v>193</v>
       </c>
       <c r="B188" s="14">
-        <v>13.3604</v>
+        <v>10.3257</v>
       </c>
       <c r="C188" s="15">
-        <v>-3.01</v>
+        <v>-8.54</v>
       </c>
       <c r="D188" s="16">
-        <v>131823</v>
+        <v>141565</v>
       </c>
       <c r="E188" s="12"/>
       <c r="F188" s="12"/>
@@ -3949,13 +3967,13 @@
         <v>194</v>
       </c>
       <c r="B189" s="14">
-        <v>13.7753</v>
+        <v>11.2894</v>
       </c>
       <c r="C189" s="15">
-        <v>2.41</v>
+        <v>-10.9</v>
       </c>
       <c r="D189" s="16">
-        <v>120727</v>
+        <v>141871</v>
       </c>
       <c r="E189" s="12"/>
       <c r="F189" s="12"/>
@@ -3965,13 +3983,13 @@
         <v>195</v>
       </c>
       <c r="B190" s="14">
-        <v>13.4515</v>
+        <v>12.6702</v>
       </c>
       <c r="C190" s="15">
-        <v>4.46</v>
+        <v>-6.98</v>
       </c>
       <c r="D190" s="16">
-        <v>130415</v>
+        <v>139960</v>
       </c>
       <c r="E190" s="12"/>
       <c r="F190" s="12"/>
@@ -3981,13 +3999,13 @@
         <v>196</v>
       </c>
       <c r="B191" s="14">
-        <v>12.8772</v>
+        <v>13.6202</v>
       </c>
       <c r="C191" s="15">
-        <v>5.03</v>
+        <v>-0.31</v>
       </c>
       <c r="D191" s="16">
-        <v>126257</v>
+        <v>139096</v>
       </c>
       <c r="E191" s="12"/>
       <c r="F191" s="12"/>
@@ -3997,13 +4015,13 @@
         <v>197</v>
       </c>
       <c r="B192" s="14">
-        <v>12.2604</v>
+        <v>13.662</v>
       </c>
       <c r="C192" s="15">
-        <v>-4.65</v>
+        <v>-0.77</v>
       </c>
       <c r="D192" s="16">
-        <v>130402</v>
+        <v>135452</v>
       </c>
       <c r="E192" s="12"/>
       <c r="F192" s="12"/>
@@ -4013,13 +4031,13 @@
         <v>198</v>
       </c>
       <c r="B193" s="14">
-        <v>12.8587</v>
+        <v>13.7682</v>
       </c>
       <c r="C193" s="15">
-        <v>3.71</v>
+        <v>3.05</v>
       </c>
       <c r="D193" s="16">
-        <v>116472</v>
+        <v>131534</v>
       </c>
       <c r="E193" s="12"/>
       <c r="F193" s="12"/>
@@ -4029,13 +4047,13 @@
         <v>199</v>
       </c>
       <c r="B194" s="14">
-        <v>12.3992</v>
+        <v>13.3604</v>
       </c>
       <c r="C194" s="15">
-        <v>6.58</v>
+        <v>-3.01</v>
       </c>
       <c r="D194" s="16">
-        <v>83474</v>
+        <v>131823</v>
       </c>
       <c r="E194" s="12"/>
       <c r="F194" s="12"/>
@@ -4045,13 +4063,13 @@
         <v>200</v>
       </c>
       <c r="B195" s="14">
-        <v>11.6337</v>
+        <v>13.7753</v>
       </c>
       <c r="C195" s="15">
-        <v>-4.02</v>
+        <v>2.41</v>
       </c>
       <c r="D195" s="16">
-        <v>82889</v>
+        <v>120727</v>
       </c>
       <c r="E195" s="12"/>
       <c r="F195" s="12"/>
@@ -4061,13 +4079,13 @@
         <v>201</v>
       </c>
       <c r="B196" s="14">
-        <v>12.1203</v>
+        <v>13.4515</v>
       </c>
       <c r="C196" s="15">
-        <v>5.98</v>
+        <v>4.46</v>
       </c>
       <c r="D196" s="16">
-        <v>82053</v>
+        <v>130415</v>
       </c>
       <c r="E196" s="12"/>
       <c r="F196" s="12"/>
@@ -4077,13 +4095,13 @@
         <v>202</v>
       </c>
       <c r="B197" s="14">
-        <v>11.4361</v>
+        <v>12.8772</v>
       </c>
       <c r="C197" s="15">
-        <v>-1.45</v>
+        <v>5.03</v>
       </c>
       <c r="D197" s="16">
-        <v>81049</v>
+        <v>126257</v>
       </c>
       <c r="E197" s="12"/>
       <c r="F197" s="12"/>
@@ -4093,13 +4111,13 @@
         <v>203</v>
       </c>
       <c r="B198" s="14">
-        <v>11.6048</v>
+        <v>12.2604</v>
       </c>
       <c r="C198" s="15">
-        <v>-5.46</v>
+        <v>-4.65</v>
       </c>
       <c r="D198" s="16">
-        <v>80218</v>
+        <v>130402</v>
       </c>
       <c r="E198" s="12"/>
       <c r="F198" s="12"/>
@@ -4109,13 +4127,13 @@
         <v>204</v>
       </c>
       <c r="B199" s="14">
-        <v>12.2754</v>
+        <v>12.8587</v>
       </c>
       <c r="C199" s="15">
-        <v>-3.45</v>
+        <v>3.71</v>
       </c>
       <c r="D199" s="16">
-        <v>82348</v>
+        <v>116472</v>
       </c>
       <c r="E199" s="12"/>
       <c r="F199" s="12"/>
@@ -4125,13 +4143,13 @@
         <v>205</v>
       </c>
       <c r="B200" s="14">
-        <v>12.7141</v>
+        <v>12.3992</v>
       </c>
       <c r="C200" s="15">
-        <v>6.98</v>
+        <v>6.58</v>
       </c>
       <c r="D200" s="16">
-        <v>81655</v>
+        <v>83474</v>
       </c>
       <c r="E200" s="12"/>
       <c r="F200" s="12"/>
@@ -4141,13 +4159,13 @@
         <v>206</v>
       </c>
       <c r="B201" s="14">
-        <v>11.8845</v>
+        <v>11.6337</v>
       </c>
       <c r="C201" s="15">
-        <v>-0.46</v>
+        <v>-4.02</v>
       </c>
       <c r="D201" s="16">
-        <v>75890</v>
+        <v>82889</v>
       </c>
       <c r="E201" s="12"/>
       <c r="F201" s="12"/>
@@ -4157,13 +4175,13 @@
         <v>207</v>
       </c>
       <c r="B202" s="14">
-        <v>11.9391</v>
+        <v>12.1203</v>
       </c>
       <c r="C202" s="15">
-        <v>-4.96</v>
+        <v>5.98</v>
       </c>
       <c r="D202" s="16">
-        <v>76219</v>
+        <v>82053</v>
       </c>
       <c r="E202" s="12"/>
       <c r="F202" s="12"/>
@@ -4173,13 +4191,13 @@
         <v>208</v>
       </c>
       <c r="B203" s="14">
-        <v>12.5625</v>
+        <v>11.4361</v>
       </c>
       <c r="C203" s="15">
-        <v>7.3</v>
+        <v>-1.45</v>
       </c>
       <c r="D203" s="16">
-        <v>76139</v>
+        <v>81049</v>
       </c>
       <c r="E203" s="12"/>
       <c r="F203" s="12"/>
@@ -4189,13 +4207,13 @@
         <v>209</v>
       </c>
       <c r="B204" s="14">
-        <v>11.7076</v>
+        <v>11.6048</v>
       </c>
       <c r="C204" s="15">
-        <v>1.96</v>
+        <v>-5.46</v>
       </c>
       <c r="D204" s="16">
-        <v>61820</v>
+        <v>80218</v>
       </c>
       <c r="E204" s="12"/>
       <c r="F204" s="12"/>
@@ -4205,13 +4223,13 @@
         <v>210</v>
       </c>
       <c r="B205" s="14">
-        <v>11.483</v>
+        <v>12.2754</v>
       </c>
       <c r="C205" s="15">
-        <v>-4.73</v>
+        <v>-3.45</v>
       </c>
       <c r="D205" s="16">
-        <v>59970</v>
+        <v>82348</v>
       </c>
       <c r="E205" s="12"/>
       <c r="F205" s="12"/>
@@ -4221,13 +4239,13 @@
         <v>211</v>
       </c>
       <c r="B206" s="14">
-        <v>12.053</v>
+        <v>12.7141</v>
       </c>
       <c r="C206" s="15">
-        <v>3.59</v>
+        <v>6.98</v>
       </c>
       <c r="D206" s="16">
-        <v>2002</v>
+        <v>81655</v>
       </c>
       <c r="E206" s="12"/>
       <c r="F206" s="12"/>
@@ -4237,13 +4255,13 @@
         <v>212</v>
       </c>
       <c r="B207" s="14">
-        <v>11.635</v>
+        <v>11.8845</v>
       </c>
       <c r="C207" s="15">
-        <v>5.73</v>
+        <v>-0.46</v>
       </c>
       <c r="D207" s="16">
-        <v>1947</v>
+        <v>75890</v>
       </c>
       <c r="E207" s="12"/>
       <c r="F207" s="12"/>
@@ -4253,13 +4271,13 @@
         <v>213</v>
       </c>
       <c r="B208" s="14">
-        <v>11.004</v>
+        <v>11.9391</v>
       </c>
       <c r="C208" s="15">
-        <v>8.56</v>
+        <v>-4.96</v>
       </c>
       <c r="D208" s="16">
-        <v>1919</v>
+        <v>76219</v>
       </c>
       <c r="E208" s="12"/>
       <c r="F208" s="12"/>
@@ -4269,13 +4287,13 @@
         <v>214</v>
       </c>
       <c r="B209" s="14">
-        <v>10.136</v>
+        <v>12.5625</v>
       </c>
       <c r="C209" s="15">
-        <v>-2.95</v>
+        <v>7.3</v>
       </c>
       <c r="D209" s="16">
-        <v>1911</v>
+        <v>76139</v>
       </c>
       <c r="E209" s="12"/>
       <c r="F209" s="12"/>
@@ -4285,13 +4303,13 @@
         <v>215</v>
       </c>
       <c r="B210" s="14">
-        <v>10.444</v>
+        <v>11.7076</v>
       </c>
       <c r="C210" s="15">
-        <v>4.44</v>
+        <v>1.96</v>
       </c>
       <c r="D210" s="16">
-        <v>232</v>
+        <v>61820</v>
       </c>
       <c r="E210" s="12"/>
       <c r="F210" s="12"/>
@@ -4301,29 +4319,125 @@
         <v>216</v>
       </c>
       <c r="B211" s="14">
-        <v>10</v>
-      </c>
-      <c r="C211" s="17" t="s">
-        <v>217</v>
+        <v>11.483</v>
+      </c>
+      <c r="C211" s="15">
+        <v>-4.73</v>
       </c>
       <c r="D211" s="16">
-        <v>0</v>
+        <v>59970</v>
       </c>
       <c r="E211" s="12"/>
       <c r="F211" s="12"/>
     </row>
-    <row r="212" ht="35" customHeight="1">
-      <c r="A212" s="18" t="s">
+    <row r="212" s="12" customFormat="1">
+      <c r="A212" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B212" s="14">
+        <v>12.053</v>
+      </c>
+      <c r="C212" s="15">
+        <v>3.59</v>
+      </c>
+      <c r="D212" s="16">
+        <v>2002</v>
+      </c>
+      <c r="E212" s="12"/>
+      <c r="F212" s="12"/>
+    </row>
+    <row r="213" s="12" customFormat="1">
+      <c r="A213" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B212" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="C212" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="D212" s="18" t="s">
-        <v>218</v>
+      <c r="B213" s="14">
+        <v>11.635</v>
+      </c>
+      <c r="C213" s="15">
+        <v>5.73</v>
+      </c>
+      <c r="D213" s="16">
+        <v>1947</v>
+      </c>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12"/>
+    </row>
+    <row r="214" s="12" customFormat="1">
+      <c r="A214" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B214" s="14">
+        <v>11.004</v>
+      </c>
+      <c r="C214" s="15">
+        <v>8.56</v>
+      </c>
+      <c r="D214" s="16">
+        <v>1919</v>
+      </c>
+      <c r="E214" s="12"/>
+      <c r="F214" s="12"/>
+    </row>
+    <row r="215" s="12" customFormat="1">
+      <c r="A215" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B215" s="14">
+        <v>10.136</v>
+      </c>
+      <c r="C215" s="15">
+        <v>-2.95</v>
+      </c>
+      <c r="D215" s="16">
+        <v>1911</v>
+      </c>
+      <c r="E215" s="12"/>
+      <c r="F215" s="12"/>
+    </row>
+    <row r="216" s="12" customFormat="1">
+      <c r="A216" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B216" s="14">
+        <v>10.444</v>
+      </c>
+      <c r="C216" s="15">
+        <v>4.44</v>
+      </c>
+      <c r="D216" s="16">
+        <v>232</v>
+      </c>
+      <c r="E216" s="12"/>
+      <c r="F216" s="12"/>
+    </row>
+    <row r="217" s="12" customFormat="1">
+      <c r="A217" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B217" s="14">
+        <v>10</v>
+      </c>
+      <c r="C217" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="D217" s="16">
+        <v>0</v>
+      </c>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+    </row>
+    <row r="218" ht="35" customHeight="1">
+      <c r="A218" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B218" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C218" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D218" s="18" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4339,18 +4453,18 @@
     <mergeCell ref="E4:E4"/>
     <mergeCell ref="E5:E5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A218:D218"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
-    <hyperlink ref="B6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
-    <hyperlink ref="C6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
-    <hyperlink ref="D6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
-    <hyperlink ref="E6" location="'Historique Cours'!A212" display="Se rendre en bas du document"/>
-    <hyperlink ref="A212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="B212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="C212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
-    <hyperlink ref="D212" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="A6" location="'Historique Cours'!A218" display="Se rendre en bas du document"/>
+    <hyperlink ref="B6" location="'Historique Cours'!A218" display="Se rendre en bas du document"/>
+    <hyperlink ref="C6" location="'Historique Cours'!A218" display="Se rendre en bas du document"/>
+    <hyperlink ref="D6" location="'Historique Cours'!A218" display="Se rendre en bas du document"/>
+    <hyperlink ref="E6" location="'Historique Cours'!A218" display="Se rendre en bas du document"/>
+    <hyperlink ref="A218" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="B218" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="C218" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
+    <hyperlink ref="D218" location="'Historique Cours'!A1" display="Se rendre en haut du document"/>
   </hyperlinks>
   <headerFooter/>
   <tableParts>
